--- a/common_rtl/009_HyperRAM_Controller/HyperRAM_Controller_CSR_Specification.xlsx
+++ b/common_rtl/009_HyperRAM_Controller/HyperRAM_Controller_CSR_Specification.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.8"/>
   <cols>
     <col width="28" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>[31:5]</t>
+          <t>[31:7]</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -1017,36 +1017,36 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="230.5" customHeight="1">
+    <row r="18" ht="248" customHeight="1">
       <c r="A18" s="21" t="n"/>
       <c r="B18" s="21" t="n"/>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>merge_en</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>[4]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>rwi</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Request merging enable. When 1, a request that continues the previous one (same direction, same chip select, next linear address) is sent inside the open HyperBus transaction without a new command and latency phase.
-Usage: program it before enable or while idle. Merging stops at the CS#-low limit of the chip select (hr_dN_tcsm.t_csm) and a new transaction starts.
-Values:
-0x0 every request starts a new HyperBus transaction;
-0x1 merge when possible (reset value).
+          <t>Resume command. Software writes 1 to leave the hold state after a timeout; hardware clears it when the controller accepts AXI requests again.
+Usage: write 1 only while hr_sts.hold = 1, after reading the log (hr_tmo_log, hr_tmo_addr) and, if needed, checking the device with the command port (hr_cmd); a write in any other state is ignored. A software write wins over the hardware clear in the same cycle.
+Values:
+0x0 no action (reset value);
+0x1 leave the hold state; reads 0x1 until the controller has resumed.
 Unit: none.
 Limits: none.</t>
         </is>
@@ -1057,25 +1057,95 @@
       <c r="B19" s="21" t="n"/>
       <c r="C19" s="21" t="inlineStr">
         <is>
+          <t>tmo_act</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>[5]</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>Timeout action. Selects what the controller does after a device timeout: stop the failed access and wait for software, or re-initialize the device by itself.
+Usage: program it before enable or while idle. With 0 the controller ends the failed access, completes the AXI request with SLVERR, enters the hold state (hr_sts.hold = 1) and holds new AXI requests until software writes hr_ctrl.resume or clears hr_ctrl.en. With 1 it runs the start-up sequence again (RESET# low for t_rp, the waits, CR0, CR1, ID0), completes every queued AXI request with SLVERR, and then accepts requests; the RAM content is lost (REQ-RST-005).
+Values:
+0x0 abort and wait for software (reset value);
+0x1 re-initialize automatically.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="230.5" customHeight="1">
+      <c r="A20" s="21" t="n"/>
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>merge_en</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>0x1</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>Request merging enable. When 1, a request that continues the previous one (same direction, same chip select, next linear address) is sent inside the open HyperBus transaction without a new command and latency phase.
+Usage: program it before enable or while idle. Merging stops at the CS#-low limit of the chip select (hr_dN_tcsm.t_csm) and a new transaction starts.
+Values:
+0x0 every request starts a new HyperBus transaction;
+0x1 merge when possible (reset value).
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="265.5" customHeight="1">
+      <c r="A21" s="21" t="n"/>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
           <t>arb_mode</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>[3:2]</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>Read and write arbitration mode. Selects which direction the controller serves first when a read and a write are both waiting for the HyperBus.
 Usage: program it before enable or while idle. A read that overlaps the bytes of an older pending write always waits for that write, whatever the mode. After 8 consecutive segments of the preferred direction one segment of the other direction is served.
@@ -1089,30 +1159,30 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="230.5" customHeight="1">
-      <c r="A20" s="21" t="n"/>
-      <c r="B20" s="21" t="n"/>
-      <c r="C20" s="21" t="inlineStr">
+    <row r="22" ht="230.5" customHeight="1">
+      <c r="A22" s="21" t="n"/>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>wr_posted</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>[1]</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>Posted write mode. Selects when the AXI write response (B channel) is returned: after the data reached the RAM, or as soon as the last write beat is stored in the controller write buffer.
 Usage: program it before enable or while the controller is idle; it is applied to writes accepted afterwards. With 1, o_idle stays low until the write buffer is empty, so wait for idle before a reset.
@@ -1124,82 +1194,22 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="248" customHeight="1">
-      <c r="A21" s="21" t="n"/>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>rw</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>Controller enable. Starts the start-up sequence of the controller: the RESET# low wait, the device wait times, the CR0 and CR1 writes and the ID0 read, after which AXI requests are accepted.
-Usage: program every timing and configuration field of the used chip selects (or load a preset) while it is 0, then write 1. Writing 1 while a field is illegal is refused and sets hr_irq_raw.cfg_err. Software writes it; reset clears it. Clearing it later stops the controller and the RAM content is lost.
-Values:
-0x0 controller disabled, RESET# held low (reset value);
-0x1 controller enabled.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20.5" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>hr_sts</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>0x4</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="22" t="n"/>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="inlineStr">
-        <is>
-          <t>HyperRAM controller status register. Shows the live state of the start-up, the AXI traffic and the device command port.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="38" customHeight="1">
+    <row r="23" ht="248" customHeight="1">
       <c r="A23" s="21" t="n"/>
       <c r="B23" s="21" t="n"/>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>[31:14]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>rw</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -1209,57 +1219,52 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="195.5" customHeight="1">
-      <c r="A24" s="21" t="n"/>
-      <c r="B24" s="21" t="n"/>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>cmd_busy</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>[13]</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>Device command busy. Reads 1 while a device register command started through hr_cmd is running.
-Usage: read-only; do not rewrite hr_cmd while it is 1. AXI requests wait while it is 1.
-Values:
-0x0 no command running;
-0x1 command running.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="178" customHeight="1">
+          <t>Controller enable. Starts the start-up sequence of the controller: the RESET# low wait, the device wait times, the CR0 and CR1 writes and the ID0 read, after which AXI requests are accepted.
+Usage: program every timing and configuration field of the used chip selects while it is 0, then write 1. Writing 1 while a field is illegal is refused and sets hr_irq_raw.cfg_err. Software writes it; reset clears it. Clearing it later stops the controller and the RAM content is lost.
+Values:
+0x0 controller disabled, RESET# held low (reset value);
+0x1 controller enabled.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20.5" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>hr_sts</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>0x4</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>HyperRAM controller status register. Shows the live state of the start-up, the AXI traffic and the device command port.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1">
       <c r="A25" s="21" t="n"/>
       <c r="B25" s="21" t="n"/>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>wr_out</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>[12:10]</t>
+          <t>[31:15]</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -1274,26 +1279,22 @@
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Outstanding writes. Number of accepted AXI writes whose B response has not been delivered yet.
-Usage: read-only; with hr_ctrl.wr_posted = 1 the value also counts posted writes still in the buffer.
-Values:
-0x0 to 0x4 number of outstanding writes.
-Unit: writes.
-Limits: at most 0x4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="178" customHeight="1">
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="213" customHeight="1">
       <c r="A26" s="21" t="n"/>
       <c r="B26" s="21" t="n"/>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>rd_out</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>[9:7]</t>
+          <t>[14]</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -1308,12 +1309,13 @@
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Outstanding reads. Number of accepted AXI reads whose last data beat has not been delivered yet.
-Usage: read-only; useful to check that the AXI side is drained.
-Values:
-0x0 to 0x4 number of outstanding reads.
-Unit: reads.
-Limits: at most 0x4.</t>
+          <t>Hold state flag. Reads 1 while the controller waits for software after a device timeout with hr_ctrl.tmo_act = 0.
+Usage: read-only; while it is 1 new AXI requests wait and the device command port still works. Leave it by writing hr_ctrl.resume, or clear hr_ctrl.en to restart with a full start-up.
+Values:
+0x0 not in hold (reset value);
+0x1 hold.
+Unit: none.
+Limits: none.</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1324,12 @@
       <c r="B27" s="21" t="n"/>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>mem_rst_n</t>
+          <t>cmd_busy</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[13]</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -1342,27 +1344,27 @@
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Memory RESET# level. Reads the level driven on the RESET# pin of the HyperRAM (active low).
-Usage: read-only; it is 0 while the controller is disabled, in reset or counting hr_dN_trst.t_rp, and 1 after the release.
-Values:
-0x0 RESET# asserted;
-0x1 RESET# released.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="195.5" customHeight="1">
+          <t>Device command busy. Reads 1 while a device register command started through hr_cmd is running.
+Usage: read-only; do not rewrite hr_cmd while it is 1. AXI requests wait while it is 1.
+Values:
+0x0 no command running;
+0x1 command running.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="178" customHeight="1">
       <c r="A28" s="21" t="n"/>
       <c r="B28" s="21" t="n"/>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>pwr_good</t>
+          <t>wr_out</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>[5]</t>
+          <t>[12:10]</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -1377,27 +1379,26 @@
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Memory power good. Level of the memory power-good input after synchronization to the core clock.
-Usage: read-only; a falling edge sets hr_irq_raw.pwr_lost and blocks AXI access until the core reset sequence is run.
-Values:
-0x0 power not good;
-0x1 power good.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="195.5" customHeight="1">
+          <t>Outstanding writes. Number of accepted AXI writes whose B response has not been delivered yet.
+Usage: read-only; with hr_ctrl.wr_posted = 1 the value also counts posted writes still in the buffer.
+Values:
+0x0 to 0x4 number of outstanding writes.
+Unit: writes.
+Limits: at most 0x4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="178" customHeight="1">
       <c r="A29" s="21" t="n"/>
       <c r="B29" s="21" t="n"/>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>cdc_busy</t>
+          <t>rd_out</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>[4]</t>
+          <t>[9:7]</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -1412,27 +1413,26 @@
       </c>
       <c r="G29" s="21" t="inlineStr">
         <is>
-          <t>APB crossing busy. Reads 1 while a request or response is in the APB to core clock-domain crossing.
-Usage: read-only; an APB-only reset is allowed only when this bit and the APB bus are idle.
-Values:
-0x0 no pending crossing;
-0x1 crossing pending.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="213" customHeight="1">
+          <t>Outstanding reads. Number of accepted AXI reads whose last data beat has not been delivered yet.
+Usage: read-only; useful to check that the AXI side is drained.
+Values:
+0x0 to 0x4 number of outstanding reads.
+Unit: reads.
+Limits: at most 0x4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="195.5" customHeight="1">
       <c r="A30" s="21" t="n"/>
       <c r="B30" s="21" t="n"/>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>cfg_valid</t>
+          <t>memrst_n</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="G30" s="21" t="inlineStr">
         <is>
-          <t>Configuration valid. Reads 1 when every timing and configuration field is inside its legal range.
-Usage: read-only; check it after programming and before writing hr_ctrl.en. When it is 0 the enable is refused and hr_irq_raw.cfg_err is set.
-Values:
-0x0 at least one field is illegal;
-0x1 all fields are legal.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="213" customHeight="1">
+          <t>Memory RESET# level. Reads the level driven on the RESET# pin of the HyperRAM (active low).
+Usage: read-only; it is 0 while the controller is disabled, in reset or counting hr_dN_trst.t_rp, and 1 after the release.
+Values:
+0x0 RESET# asserted;
+0x1 RESET# released.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="195.5" customHeight="1">
       <c r="A31" s="21" t="n"/>
       <c r="B31" s="21" t="n"/>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>idle</t>
+          <t>pwr_good</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -1482,27 +1482,27 @@
       </c>
       <c r="G31" s="21" t="inlineStr">
         <is>
-          <t>Controller idle. Same condition as the o_idle output: all accepted work is finished, the write buffer is empty, no command runs and CS# is high.
-Usage: read-only; the SoC reset logic waits for 1 before it asserts the core reset (the APB side stays out of this wait).
-Values:
-0x0 busy or not initialized;
-0x1 idle.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="195.5" customHeight="1">
+          <t>Memory power good. Level of the memory power-good input after synchronization to the core clock.
+Usage: read-only; a falling edge sets hr_irq_raw.pwr_lost and blocks AXI access until the core reset sequence is run.
+Values:
+0x0 power not good;
+0x1 power good.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1">
       <c r="A32" s="21" t="n"/>
       <c r="B32" s="21" t="n"/>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>init_done</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>[4]</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -1517,27 +1517,22 @@
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
-          <t>Initialization done. Reads 1 when the start-up sequence has completed and the controller accepts AXI requests and device commands.
-Usage: read-only; wait for 1 before any AXI access or hr_cmd command. A core reset or clearing hr_ctrl.en returns it to 0.
-Values:
-0x0 not ready;
-0x1 ready.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="195.5" customHeight="1">
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="213" customHeight="1">
       <c r="A33" s="21" t="n"/>
       <c r="B33" s="21" t="n"/>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>init_busy</t>
+          <t>cfg_valid</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[3]</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -1552,52 +1547,62 @@
       </c>
       <c r="G33" s="21" t="inlineStr">
         <is>
-          <t>Start-up busy. Reads 1 while the controller runs the RESET#, wait, CR0, CR1 and ID0 sequence after enable.
-Usage: read-only; poll it after writing hr_ctrl.en. It falls to 0 when hr_sts.init_done rises.
-Values:
-0x0 not running;
-0x1 start-up running.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20.5" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>hr_cap</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>0x8</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="inlineStr">
-        <is>
-          <t>0x00000004</t>
-        </is>
-      </c>
-      <c r="G34" s="22" t="inlineStr">
-        <is>
-          <t>HyperRAM controller capability register. Reports the elaboration parameters of this build.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="38" customHeight="1">
+          <t>Configuration valid. Reads 1 when every timing and configuration field is inside its legal range.
+Usage: read-only; check it after programming and before writing hr_ctrl.en. When it is 0 the enable is refused and hr_irq_raw.cfg_err is set.
+Values:
+0x0 at least one field is illegal;
+0x1 all fields are legal.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="213" customHeight="1">
+      <c r="A34" s="21" t="n"/>
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>Controller idle. Same condition as the o_idle output: all accepted work is finished, the write buffer is empty, no command runs and CS# is high.
+Usage: read-only; the SoC reset logic waits for 1 before it asserts the core reset (the APB side stays out of this wait).
+Values:
+0x0 busy or not initialized;
+0x1 idle.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="195.5" customHeight="1">
       <c r="A35" s="21" t="n"/>
       <c r="B35" s="21" t="n"/>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>init_done</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>[31:8]</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -1612,35 +1617,130 @@
       </c>
       <c r="G35" s="21" t="inlineStr">
         <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="178" customHeight="1">
+          <t>Initialization done. Reads 1 when the start-up sequence has completed and the controller accepts AXI requests and device commands.
+Usage: read-only; wait for 1 before any AXI access or hr_cmd command. A core reset or clearing hr_ctrl.en returns it to 0.
+Values:
+0x0 not ready;
+0x1 ready.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="195.5" customHeight="1">
       <c r="A36" s="21" t="n"/>
       <c r="B36" s="21" t="n"/>
       <c r="C36" s="21" t="inlineStr">
         <is>
+          <t>init_busy</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>Start-up busy. Reads 1 while the controller runs the RESET#, wait, CR0, CR1 and ID0 sequence after enable.
+Usage: read-only; poll it after writing hr_ctrl.en. It falls to 0 when hr_sts.init_done rises.
+Values:
+0x0 not running;
+0x1 start-up running.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20.5" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>hr_cap</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>0x8</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>0x00000004</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>HyperRAM controller capability register. Reports the elaboration parameters of this build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="38" customHeight="1">
+      <c r="A38" s="21" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>[31:8]</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="178" customHeight="1">
+      <c r="A39" s="21" t="n"/>
+      <c r="B39" s="21" t="n"/>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
           <t>dly_w</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D39" s="21" t="inlineStr">
         <is>
           <t>[7:4]</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G36" s="21" t="inlineStr">
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
         <is>
           <t>Delay-line select width. Reports the width of the delay-line tap select, PARA_DLY_TAP_W.
 Usage: read-only; the field hr_dN_rcap.tap uses only this many low bits.
@@ -1651,30 +1751,30 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="195.5" customHeight="1">
-      <c r="A37" s="21" t="n"/>
-      <c r="B37" s="21" t="n"/>
-      <c r="C37" s="21" t="inlineStr">
+    <row r="40" ht="195.5" customHeight="1">
+      <c r="A40" s="21" t="n"/>
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>num_cs</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D40" s="21" t="inlineStr">
         <is>
           <t>[3:2]</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="E40" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
         <is>
           <t>0x1</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G40" s="21" t="inlineStr">
         <is>
           <t>Number of chip selects. Reports the parameter PARA_NUM_CS.
 Usage: read-only; program the register group hr_d1_* only when it is 2.
@@ -1686,125 +1786,125 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="195.5" customHeight="1">
-      <c r="A38" s="21" t="n"/>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>mem_x16</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>[1]</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G38" s="21" t="inlineStr">
-        <is>
-          <t>Memory width. Reports the HyperBus profile chosen with the parameter PARA_MEM_DQ_W.
-Usage: read-only; select the device preset that matches this width.
-Values:
-0x0 x8 HyperBus;
-0x1 x16 Extended-I/O.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="195.5" customHeight="1">
-      <c r="A39" s="21" t="n"/>
-      <c r="B39" s="21" t="n"/>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>axi_w64</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F39" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G39" s="21" t="inlineStr">
-        <is>
-          <t>AXI data width. Reports the width chosen with the parameter PARA_AXI_DATA_W.
-Usage: read-only; software uses it to size its AXI accesses.
-Values:
-0x0 32-bit AXI data;
-0x1 64-bit AXI data.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20.5" customHeight="1">
-      <c r="A40" s="22" t="inlineStr">
-        <is>
-          <t>hr_size</t>
-        </is>
-      </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>0xC</t>
-        </is>
-      </c>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="22" t="n"/>
-      <c r="F40" s="22" t="inlineStr">
-        <is>
-          <t>0x02000000</t>
-        </is>
-      </c>
-      <c r="G40" s="22" t="inlineStr">
-        <is>
-          <t>HyperRAM aperture size register. Reports the byte capacity of one chip select.</t>
-        </is>
-      </c>
-    </row>
     <row r="41" ht="195.5" customHeight="1">
       <c r="A41" s="21" t="n"/>
       <c r="B41" s="21" t="n"/>
       <c r="C41" s="21" t="inlineStr">
         <is>
+          <t>mem_x16</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
+        <is>
+          <t>Memory width. Reports the HyperBus profile chosen with the parameter PARA_MEM_DQ_W.
+Usage: read-only; select the device values that match this width.
+Values:
+0x0 x8 HyperBus;
+0x1 x16 Extended-I/O.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="195.5" customHeight="1">
+      <c r="A42" s="21" t="n"/>
+      <c r="B42" s="21" t="n"/>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>axi_w64</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>AXI data width. Reports the width chosen with the parameter PARA_AXI_DATA_W.
+Usage: read-only; software uses it to size its AXI accesses.
+Values:
+0x0 32-bit AXI data;
+0x1 64-bit AXI data.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20.5" customHeight="1">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>hr_size</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>0xC</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>0x02000000</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>HyperRAM aperture size register. Reports the byte capacity of one chip select.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="195.5" customHeight="1">
+      <c r="A44" s="21" t="n"/>
+      <c r="B44" s="21" t="n"/>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
           <t>bytes</t>
         </is>
       </c>
-      <c r="D41" s="21" t="inlineStr">
+      <c r="D44" s="21" t="inlineStr">
         <is>
           <t>[31:0]</t>
         </is>
       </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F41" s="21" t="inlineStr">
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
         <is>
           <t>0x2000000</t>
         </is>
       </c>
-      <c r="G41" s="21" t="inlineStr">
+      <c r="G44" s="21" t="inlineStr">
         <is>
           <t>Aperture size of one chip select. Reports the parameter PARA_MEM_SIZE_BYTES, the size of the AXI address window that maps to one device.
 Usage: read-only; the second chip select starts at this offset in the AXI window.
@@ -1815,155 +1915,155 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="20.5" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
+    <row r="45" ht="20.5" customHeight="1">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>hr_clk</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
+      <c r="B45" s="22" t="inlineStr">
         <is>
           <t>0x10</t>
         </is>
       </c>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="22" t="n"/>
-      <c r="E42" s="22" t="n"/>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="22" t="inlineStr">
         <is>
           <t>0x00000002</t>
         </is>
       </c>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="G45" s="22" t="inlineStr">
         <is>
           <t>HyperBus clock register. Sets the clock divider, the clock type and the clock phase of the memory interface.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="21" t="n"/>
-      <c r="B43" s="21" t="n"/>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>reserved</t>
-        </is>
-      </c>
-      <c r="D43" s="21" t="inlineStr">
-        <is>
-          <t>[31:10]</t>
-        </is>
-      </c>
-      <c r="E43" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F43" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G43" s="21" t="inlineStr">
-        <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="213" customHeight="1">
-      <c r="A44" s="21" t="n"/>
-      <c r="B44" s="21" t="n"/>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>ck_phase</t>
-        </is>
-      </c>
-      <c r="D44" s="21" t="inlineStr">
-        <is>
-          <t>[9]</t>
-        </is>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>rw</t>
-        </is>
-      </c>
-      <c r="F44" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G44" s="21" t="inlineStr">
-        <is>
-          <t>CK phase select. Chooses the core clock edge on which CK toggles, which sets the offset between CK and the write data.
-Usage: program it while hr_ctrl.en = 0. With 0 the CK edge lies in the middle of each write data interval (1.25 ns from the data change at 200 MHz); with 1 CK and data change on the same edge.
-Values:
-0x0 CK toggles on the falling core clock edge (reset value);
-0x1 CK toggles on the rising edge.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="213" customHeight="1">
-      <c r="A45" s="21" t="n"/>
-      <c r="B45" s="21" t="n"/>
-      <c r="C45" s="21" t="inlineStr">
-        <is>
-          <t>ck_diff</t>
-        </is>
-      </c>
-      <c r="D45" s="21" t="inlineStr">
-        <is>
-          <t>[8]</t>
-        </is>
-      </c>
-      <c r="E45" s="21" t="inlineStr">
-        <is>
-          <t>rw</t>
-        </is>
-      </c>
-      <c r="F45" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G45" s="21" t="inlineStr">
-        <is>
-          <t>Differential clock enable. Selects whether the controller drives the complementary clock CK# or leaves it high; it is also written into CR1[6] of the device.
-Usage: program it while hr_ctrl.en = 0, before the start-up writes CR1; the devices must support the chosen clock type.
-Values:
-0x0 single-ended CK, CK# held high (reset value);
-0x1 differential CK and CK#.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="213" customHeight="1">
+    <row r="46" ht="38" customHeight="1">
       <c r="A46" s="21" t="n"/>
       <c r="B46" s="21" t="n"/>
       <c r="C46" s="21" t="inlineStr">
         <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>[31:10]</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="213" customHeight="1">
+      <c r="A47" s="21" t="n"/>
+      <c r="B47" s="21" t="n"/>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>ck_phase</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>[9]</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t>CK phase select. Chooses the core clock edge on which CK toggles, which sets the offset between CK and the write data.
+Usage: program it while hr_ctrl.en = 0. With 0 the CK edge lies in the middle of each write data interval (1.25 ns from the data change at 200 MHz); with 1 CK and data change on the same edge.
+Values:
+0x0 CK toggles on the falling core clock edge (reset value);
+0x1 CK toggles on the rising edge.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="213" customHeight="1">
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="21" t="n"/>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>ck_diff</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>[8]</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G48" s="21" t="inlineStr">
+        <is>
+          <t>Differential clock enable. Selects whether the controller drives the complementary clock CK# or leaves it high; it is also written into CR1[6] of the device.
+Usage: program it while hr_ctrl.en = 0, before the start-up writes CR1; the devices must support the chosen clock type.
+Values:
+0x0 single-ended CK, CK# held high (reset value);
+0x1 differential CK and CK#.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="213" customHeight="1">
+      <c r="A49" s="21" t="n"/>
+      <c r="B49" s="21" t="n"/>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
           <t>ck_div</t>
         </is>
       </c>
-      <c r="D46" s="21" t="inlineStr">
+      <c r="D49" s="21" t="inlineStr">
         <is>
           <t>[7:0]</t>
         </is>
       </c>
-      <c r="E46" s="21" t="inlineStr">
+      <c r="E49" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F46" s="21" t="inlineStr">
+      <c r="F49" s="21" t="inlineStr">
         <is>
           <t>0x2</t>
         </is>
       </c>
-      <c r="G46" s="21" t="inlineStr">
+      <c r="G49" s="21" t="inlineStr">
         <is>
           <t>HyperBus clock divider. Number of core clock cycles in one HyperBus CK period; CK is the core clock divided by this value.
 Usage: program it while hr_ctrl.en = 0 and rescale every timing count (they are counted in CK periods) when you change it. 2 gives CK = 200 MHz for a 400 MHz core clock.
@@ -1975,147 +2075,47 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="20.5" customHeight="1">
-      <c r="A47" s="22" t="inlineStr">
+    <row r="50" ht="20.5" customHeight="1">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>hr_cmd</t>
         </is>
       </c>
-      <c r="B47" s="22" t="inlineStr">
+      <c r="B50" s="22" t="inlineStr">
         <is>
           <t>0x14</t>
         </is>
       </c>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n"/>
-      <c r="E47" s="22" t="n"/>
-      <c r="F47" s="22" t="inlineStr">
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="22" t="n"/>
+      <c r="F50" s="22" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
-      <c r="G47" s="22" t="inlineStr">
+      <c r="G50" s="22" t="inlineStr">
         <is>
           <t>Device register command register. Starts a read or a write of one register of the HyperRAM device.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="38" customHeight="1">
-      <c r="A48" s="21" t="n"/>
-      <c r="B48" s="21" t="n"/>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>reserved</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>[31:3]</t>
-        </is>
-      </c>
-      <c r="E48" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F48" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G48" s="21" t="inlineStr">
-        <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="195.5" customHeight="1">
-      <c r="A49" s="21" t="n"/>
-      <c r="B49" s="21" t="n"/>
-      <c r="C49" s="21" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="D49" s="21" t="inlineStr">
-        <is>
-          <t>[2]</t>
-        </is>
-      </c>
-      <c r="E49" s="21" t="inlineStr">
-        <is>
-          <t>rw</t>
-        </is>
-      </c>
-      <c r="F49" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G49" s="21" t="inlineStr">
-        <is>
-          <t>Command chip select. Selects the chip select (device) that receives the command.
-Usage: program it before writing hr_cmd.go; value 1 is legal only when hr_cap.num_cs is 2.
-Values:
-0x0 chip select 0;
-0x1 chip select 1.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="213" customHeight="1">
-      <c r="A50" s="21" t="n"/>
-      <c r="B50" s="21" t="n"/>
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>wr</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>[1]</t>
-        </is>
-      </c>
-      <c r="E50" s="21" t="inlineStr">
-        <is>
-          <t>rw</t>
-        </is>
-      </c>
-      <c r="F50" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G50" s="21" t="inlineStr">
-        <is>
-          <t>Command direction. Selects whether the command reads or writes the device register.
-Usage: program it before writing hr_cmd.go. A write sends hr_cmd_wdata with zero latency; a read waits the programmed latency and captures one word into hr_cmd_rdata.rdata.
-Values:
-0x0 read the register;
-0x1 write the register.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="213" customHeight="1">
+    <row r="51" ht="38" customHeight="1">
       <c r="A51" s="21" t="n"/>
       <c r="B51" s="21" t="n"/>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>go</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="D51" s="21" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[31:3]</t>
         </is>
       </c>
       <c r="E51" s="21" t="inlineStr">
         <is>
-          <t>rwi</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="F51" s="21" t="inlineStr">
@@ -2125,52 +2125,57 @@
       </c>
       <c r="G51" s="21" t="inlineStr">
         <is>
-          <t>Command start. Starting bit of a device register command; hardware clears it when the command has finished.
-Usage: first write hr_cmd_addr, hr_cmd_wdata (for a write), hr_cmd.wr and hr_cmd.cs, then write 1 here, only when hr_sts.cmd_busy = 0. A software write wins over the hardware clear in the same cycle, so do not rewrite the register while the command runs.
-Values:
-0x0 no command running (reset value);
-0x1 start the command; reads 0x1 until the command is done.
-Unit: none.
-Limits: a command before hr_sts.init_done = 1 is rejected and sets hr_cmd_rdata.err.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20.5" customHeight="1">
-      <c r="A52" s="22" t="inlineStr">
-        <is>
-          <t>hr_cmd_addr</t>
-        </is>
-      </c>
-      <c r="B52" s="22" t="inlineStr">
-        <is>
-          <t>0x18</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="E52" s="22" t="n"/>
-      <c r="F52" s="22" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="G52" s="22" t="inlineStr">
-        <is>
-          <t>Device register address register. Holds the address of the device register for a command.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="195.5" customHeight="1">
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="195.5" customHeight="1">
+      <c r="A52" s="21" t="n"/>
+      <c r="B52" s="21" t="n"/>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>cs</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="inlineStr">
+        <is>
+          <t>Command chip select. Selects the chip select (device) that receives the command.
+Usage: program it before writing hr_cmd.go; value 1 is legal only when hr_cap.num_cs is 2.
+Values:
+0x0 chip select 0;
+0x1 chip select 1.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="213" customHeight="1">
       <c r="A53" s="21" t="n"/>
       <c r="B53" s="21" t="n"/>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>addr</t>
+          <t>wr</t>
         </is>
       </c>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>[31:0]</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="E53" s="21" t="inlineStr">
@@ -2185,67 +2190,73 @@
       </c>
       <c r="G53" s="21" t="inlineStr">
         <is>
-          <t>Device register address. Word address sent in the command and address phase with the register-space bit set.
-Usage: program it before writing hr_cmd.go; the register addresses (for example ID0, ID1, CR0 and CR1) are given in the device datasheet.
-Values:
-0x00000000 to 0xFFFFFFFF word address of the device register space.
-Unit: 16-bit words.
-Limits: use only addresses that the device defines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20.5" customHeight="1">
-      <c r="A54" s="22" t="inlineStr">
-        <is>
-          <t>hr_cmd_wdata</t>
-        </is>
-      </c>
-      <c r="B54" s="22" t="inlineStr">
-        <is>
-          <t>0x1C</t>
-        </is>
-      </c>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="22" t="n"/>
-      <c r="E54" s="22" t="n"/>
-      <c r="F54" s="22" t="inlineStr">
+          <t>Command direction. Selects whether the command reads or writes the device register.
+Usage: program it before writing hr_cmd.go. A write sends hr_cmd_wdata with zero latency; a read waits the programmed latency and captures one word into hr_cmd_rdata.rdata.
+Values:
+0x0 read the register;
+0x1 write the register.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="213" customHeight="1">
+      <c r="A54" s="21" t="n"/>
+      <c r="B54" s="21" t="n"/>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>go</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>rwi</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
+          <t>Command start. Starting bit of a device register command; hardware clears it when the command has finished.
+Usage: first write hr_cmd_addr, hr_cmd_wdata (for a write), hr_cmd.wr and hr_cmd.cs, then write 1 here, only when hr_sts.cmd_busy = 0. A software write wins over the hardware clear in the same cycle, so do not rewrite the register while the command runs.
+Values:
+0x0 no command running (reset value);
+0x1 start the command; reads 0x1 until the command is done.
+Unit: none.
+Limits: a command before hr_sts.init_done = 1 is rejected and sets hr_cmd_rdata.err.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20.5" customHeight="1">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>hr_cmd_addr</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>0x18</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="22" t="n"/>
+      <c r="F55" s="22" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
-      <c r="G54" s="22" t="inlineStr">
-        <is>
-          <t>Device register write data register. Holds the data of a device register write command.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="38" customHeight="1">
-      <c r="A55" s="21" t="n"/>
-      <c r="B55" s="21" t="n"/>
-      <c r="C55" s="21" t="inlineStr">
-        <is>
-          <t>reserved</t>
-        </is>
-      </c>
-      <c r="D55" s="21" t="inlineStr">
-        <is>
-          <t>[31:16]</t>
-        </is>
-      </c>
-      <c r="E55" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F55" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G55" s="21" t="inlineStr">
-        <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
+      <c r="G55" s="22" t="inlineStr">
+        <is>
+          <t>Device register address register. Holds the address of the device register for a command.</t>
         </is>
       </c>
     </row>
@@ -2254,12 +2265,12 @@
       <c r="B56" s="21" t="n"/>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>wdata</t>
+          <t>addr</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
         <is>
-          <t>[15:0]</t>
+          <t>[31:0]</t>
         </is>
       </c>
       <c r="E56" s="21" t="inlineStr">
@@ -2274,24 +2285,24 @@
       </c>
       <c r="G56" s="21" t="inlineStr">
         <is>
-          <t>Device register write data. The 16-bit value written into the device register by a write command.
-Usage: program it before writing hr_cmd.go with hr_cmd.wr = 1; unused for a read command.
-Values:
-0x0000 to 0xFFFF data of the register write.
-Unit: none.
-Limits: write reserved device fields with their default value; writing CR0[7:4] differently from hr_dN_cfg.init_lat sets hr_irq_raw.lat_mis.</t>
+          <t>Device register address. Word address sent in the command and address phase with the register-space bit set.
+Usage: program it before writing hr_cmd.go; the register addresses (for example ID0, ID1, CR0 and CR1) are given in the device datasheet.
+Values:
+0x00000000 to 0xFFFFFFFF word address of the device register space.
+Unit: 16-bit words.
+Limits: use only addresses that the device defines.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20.5" customHeight="1">
       <c r="A57" s="22" t="inlineStr">
         <is>
-          <t>hr_cmd_rdata</t>
+          <t>hr_cmd_wdata</t>
         </is>
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>0x20</t>
+          <t>0x1C</t>
         </is>
       </c>
       <c r="C57" s="22" t="n"/>
@@ -2304,7 +2315,7 @@
       </c>
       <c r="G57" s="22" t="inlineStr">
         <is>
-          <t>Device register read data register. Returns the data of a device register read command and its completion flags.</t>
+          <t>Device register write data register. Holds the data of a device register write command.</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2329,7 @@
       </c>
       <c r="D58" s="21" t="inlineStr">
         <is>
-          <t>[31:18]</t>
+          <t>[31:16]</t>
         </is>
       </c>
       <c r="E58" s="21" t="inlineStr">
@@ -2343,17 +2354,17 @@
       <c r="B59" s="21" t="n"/>
       <c r="C59" s="21" t="inlineStr">
         <is>
-          <t>err</t>
+          <t>wdata</t>
         </is>
       </c>
       <c r="D59" s="21" t="inlineStr">
         <is>
-          <t>[17]</t>
+          <t>[15:0]</t>
         </is>
       </c>
       <c r="E59" s="21" t="inlineStr">
         <is>
-          <t>w1c</t>
+          <t>rw</t>
         </is>
       </c>
       <c r="F59" s="21" t="inlineStr">
@@ -2363,62 +2374,51 @@
       </c>
       <c r="G59" s="21" t="inlineStr">
         <is>
-          <t>Command error flag. Hardware sets it when a command is rejected because the controller is not initialized.
-Usage: check it when hr_cmd_rdata.done does not rise; write 1 to clear.
-Values:
-0x0 no error;
-0x1 command rejected.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="213" customHeight="1">
-      <c r="A60" s="21" t="n"/>
-      <c r="B60" s="21" t="n"/>
-      <c r="C60" s="21" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="D60" s="21" t="inlineStr">
-        <is>
-          <t>[16]</t>
-        </is>
-      </c>
-      <c r="E60" s="21" t="inlineStr">
-        <is>
-          <t>w1c</t>
-        </is>
-      </c>
-      <c r="F60" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G60" s="21" t="inlineStr">
-        <is>
-          <t>Command done flag. Hardware sets it when a device register command has completed; software clears it.
-Usage: poll it or use hr_irq_raw.cmd_done; write 1 to clear before the next command. A hardware set in the same cycle as the clear wins.
-Values:
-0x0 no completed command;
-0x1 command completed.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="178" customHeight="1">
+          <t>Device register write data. The 16-bit value written into the device register by a write command.
+Usage: program it before writing hr_cmd.go with hr_cmd.wr = 1; unused for a read command.
+Values:
+0x0000 to 0xFFFF data of the register write.
+Unit: none.
+Limits: write reserved device fields with their default value; writing CR0[7:4] differently from hr_dN_cfg.init_lat sets hr_irq_raw.lat_mis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20.5" customHeight="1">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>hr_cmd_rdata</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>0x20</t>
+        </is>
+      </c>
+      <c r="C60" s="22" t="n"/>
+      <c r="D60" s="22" t="n"/>
+      <c r="E60" s="22" t="n"/>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr">
+        <is>
+          <t>Device register read data register. Returns the data of a device register read command and its completion flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="38" customHeight="1">
       <c r="A61" s="21" t="n"/>
       <c r="B61" s="21" t="n"/>
       <c r="C61" s="21" t="inlineStr">
         <is>
-          <t>rdata</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="D61" s="21" t="inlineStr">
         <is>
-          <t>[15:0]</t>
+          <t>[31:18]</t>
         </is>
       </c>
       <c r="E61" s="21" t="inlineStr">
@@ -2433,56 +2433,62 @@
       </c>
       <c r="G61" s="21" t="inlineStr">
         <is>
-          <t>Device register read data. The 16-bit word captured by the last read command.
-Usage: read it after hr_cmd_rdata.done is 1; its content is not defined before.
-Values:
-0x0000 to 0xFFFF content of the device register.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20.5" customHeight="1">
-      <c r="A62" s="22" t="inlineStr">
-        <is>
-          <t>hr_irq_raw</t>
-        </is>
-      </c>
-      <c r="B62" s="22" t="inlineStr">
-        <is>
-          <t>0x24</t>
-        </is>
-      </c>
-      <c r="C62" s="22" t="n"/>
-      <c r="D62" s="22" t="n"/>
-      <c r="E62" s="22" t="n"/>
-      <c r="F62" s="22" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="inlineStr">
-        <is>
-          <t>Raw interrupt status register. Holds the sticky event flags of the controller before masking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="38" customHeight="1">
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="195.5" customHeight="1">
+      <c r="A62" s="21" t="n"/>
+      <c r="B62" s="21" t="n"/>
+      <c r="C62" s="21" t="inlineStr">
+        <is>
+          <t>err</t>
+        </is>
+      </c>
+      <c r="D62" s="21" t="inlineStr">
+        <is>
+          <t>[17]</t>
+        </is>
+      </c>
+      <c r="E62" s="21" t="inlineStr">
+        <is>
+          <t>w1c</t>
+        </is>
+      </c>
+      <c r="F62" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G62" s="21" t="inlineStr">
+        <is>
+          <t>Command error flag. Hardware sets it when a command is rejected because the controller is not initialized.
+Usage: check it when hr_cmd_rdata.done does not rise; write 1 to clear.
+Values:
+0x0 no error;
+0x1 command rejected.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="213" customHeight="1">
       <c r="A63" s="21" t="n"/>
       <c r="B63" s="21" t="n"/>
       <c r="C63" s="21" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>done</t>
         </is>
       </c>
       <c r="D63" s="21" t="inlineStr">
         <is>
-          <t>[31:8]</t>
+          <t>[16]</t>
         </is>
       </c>
       <c r="E63" s="21" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>w1c</t>
         </is>
       </c>
       <c r="F63" s="21" t="inlineStr">
@@ -2492,27 +2498,32 @@
       </c>
       <c r="G63" s="21" t="inlineStr">
         <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="195.5" customHeight="1">
+          <t>Command done flag. Hardware sets it when a device register command has completed; software clears it.
+Usage: poll it or use hr_irq_raw.cmd_done; write 1 to clear before the next command. A hardware set in the same cycle as the clear wins.
+Values:
+0x0 no completed command;
+0x1 command completed.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="178" customHeight="1">
       <c r="A64" s="21" t="n"/>
       <c r="B64" s="21" t="n"/>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>cmd_done</t>
+          <t>rdata</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
         <is>
-          <t>[7]</t>
+          <t>[15:0]</t>
         </is>
       </c>
       <c r="E64" s="21" t="inlineStr">
         <is>
-          <t>w1c</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="F64" s="21" t="inlineStr">
@@ -2522,67 +2533,56 @@
       </c>
       <c r="G64" s="21" t="inlineStr">
         <is>
-          <t>Device command done event. Set when a device register command has completed.
-Usage: together with hr_cmd_rdata.done; write 1 to clear.
-Values:
-0x0 no event;
-0x1 event occurred.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="195.5" customHeight="1">
-      <c r="A65" s="21" t="n"/>
-      <c r="B65" s="21" t="n"/>
-      <c r="C65" s="21" t="inlineStr">
-        <is>
-          <t>lat_mis</t>
-        </is>
-      </c>
-      <c r="D65" s="21" t="inlineStr">
-        <is>
-          <t>[6]</t>
-        </is>
-      </c>
-      <c r="E65" s="21" t="inlineStr">
-        <is>
-          <t>w1c</t>
-        </is>
-      </c>
-      <c r="F65" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G65" s="21" t="inlineStr">
-        <is>
-          <t>Latency mismatch event. Set when a device register write changes CR0[7:4] to a latency code that differs from hr_dN_cfg.init_lat.
-Usage: the controller keeps its own latency; restore CR0 or change init_lat while disabled; write 1 to clear.
-Values:
-0x0 no event;
-0x1 event occurred.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="195.5" customHeight="1">
+          <t>Device register read data. The 16-bit word captured by the last read command.
+Usage: read it after hr_cmd_rdata.done is 1; its content is not defined before.
+Values:
+0x0000 to 0xFFFF content of the device register.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20.5" customHeight="1">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>hr_irq_raw</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>0x24</t>
+        </is>
+      </c>
+      <c r="C65" s="22" t="n"/>
+      <c r="D65" s="22" t="n"/>
+      <c r="E65" s="22" t="n"/>
+      <c r="F65" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr">
+        <is>
+          <t>Raw interrupt status register. Holds the sticky event flags of the controller before masking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="38" customHeight="1">
       <c r="A66" s="21" t="n"/>
       <c r="B66" s="21" t="n"/>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>id_mis</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
         <is>
-          <t>[5]</t>
+          <t>[31:9]</t>
         </is>
       </c>
       <c r="E66" s="21" t="inlineStr">
         <is>
-          <t>w1c</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="F66" s="21" t="inlineStr">
@@ -2592,27 +2592,22 @@
       </c>
       <c r="G66" s="21" t="inlineStr">
         <is>
-          <t>ID mismatch event. Set when the ID0 value read after start-up differs from hr_dN_id.id0_exp of that chip select.
-Usage: only active when hr_dN_id.id_chk_en = 1; AXI access is not blocked; write 1 to clear.
-Values:
-0x0 no event;
-0x1 event occurred.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="195.5" customHeight="1">
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="230.5" customHeight="1">
       <c r="A67" s="21" t="n"/>
       <c r="B67" s="21" t="n"/>
       <c r="C67" s="21" t="inlineStr">
         <is>
-          <t>pwr_lost</t>
+          <t>tmo</t>
         </is>
       </c>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>[4]</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="E67" s="21" t="inlineStr">
@@ -2627,8 +2622,8 @@
       </c>
       <c r="G67" s="21" t="inlineStr">
         <is>
-          <t>Power loss event. Set when the synchronized memory power-good signal falls.
-Usage: run the reset sequence of the SoC; accepted work may not complete; write 1 to clear.
+          <t>Device timeout event. Set when the device did not answer within the wait time of hr_dN_tmo.t_tmo, for example no read data strobe after the initial latency.
+Usage: read hr_tmo_log and hr_tmo_addr to find the command, the address and the step that was waited for; then act as hr_ctrl.tmo_act selects; write 1 to clear. The log stays until hr_tmo_log.valid is cleared.
 Values:
 0x0 no event;
 0x1 event occurred.
@@ -2642,12 +2637,12 @@
       <c r="B68" s="21" t="n"/>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>slverr</t>
+          <t>cmd_done</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="E68" s="21" t="inlineStr">
@@ -2662,8 +2657,8 @@
       </c>
       <c r="G68" s="21" t="inlineStr">
         <is>
-          <t>AXI slave error event. Set when a request with an unsupported burst type (FIXED) is answered with SLVERR.
-Usage: details are in hr_err_ri and hr_err_wi; write 1 to clear.
+          <t>Device command done event. Set when a device register command has completed.
+Usage: together with hr_cmd_rdata.done; write 1 to clear.
 Values:
 0x0 no event;
 0x1 event occurred.
@@ -2677,12 +2672,12 @@
       <c r="B69" s="21" t="n"/>
       <c r="C69" s="21" t="inlineStr">
         <is>
-          <t>decerr</t>
+          <t>lat_mis</t>
         </is>
       </c>
       <c r="D69" s="21" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="E69" s="21" t="inlineStr">
@@ -2697,8 +2692,8 @@
       </c>
       <c r="G69" s="21" t="inlineStr">
         <is>
-          <t>AXI decode error event. Set when a request addresses bytes outside the aperture and is answered with DECERR.
-Usage: the address and ID of the request are in hr_err_ra and hr_err_wa; write 1 to clear.
+          <t>Latency mismatch event. Set when a device register write changes CR0[7:4] to a latency code that differs from hr_dN_cfg.init_lat.
+Usage: the controller keeps its own latency; restore CR0 or change init_lat while disabled; write 1 to clear.
 Values:
 0x0 no event;
 0x1 event occurred.
@@ -2707,17 +2702,17 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="213" customHeight="1">
+    <row r="70" ht="195.5" customHeight="1">
       <c r="A70" s="21" t="n"/>
       <c r="B70" s="21" t="n"/>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>cfg_err</t>
+          <t>id_mis</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="E70" s="21" t="inlineStr">
@@ -2732,8 +2727,8 @@
       </c>
       <c r="G70" s="21" t="inlineStr">
         <is>
-          <t>Configuration error event. Set when hr_ctrl.en is written with an illegal field, or when a preset load is written while the controller is enabled.
-Usage: read hr_sts.cfg_valid to find that a field is illegal; correct the field and write hr_ctrl.en again; write 1 to clear.
+          <t>ID mismatch event. Set when the ID0 value read after start-up differs from hr_dN_id.id0_exp of that chip select.
+Usage: only active when hr_dN_id.id_chk_en = 1; AXI access is not blocked; write 1 to clear.
 Values:
 0x0 no event;
 0x1 event occurred.
@@ -2747,12 +2742,12 @@
       <c r="B71" s="21" t="n"/>
       <c r="C71" s="21" t="inlineStr">
         <is>
-          <t>init_ok</t>
+          <t>pwr_lost</t>
         </is>
       </c>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[4]</t>
         </is>
       </c>
       <c r="E71" s="21" t="inlineStr">
@@ -2767,8 +2762,8 @@
       </c>
       <c r="G71" s="21" t="inlineStr">
         <is>
-          <t>Initialization complete event. Set when the start-up sequence has finished.
-Usage: enable it in hr_irq_en to get an interrupt instead of polling hr_sts.init_done; write 1 to clear.
+          <t>Power loss event. Set when the synchronized memory power-good signal falls.
+Usage: run the reset sequence of the SoC; accepted work may not complete; write 1 to clear.
 Values:
 0x0 no event;
 0x1 event occurred.
@@ -2777,47 +2772,57 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="20.5" customHeight="1">
-      <c r="A72" s="22" t="inlineStr">
-        <is>
-          <t>hr_irq_en</t>
-        </is>
-      </c>
-      <c r="B72" s="22" t="inlineStr">
-        <is>
-          <t>0x28</t>
-        </is>
-      </c>
-      <c r="C72" s="22" t="n"/>
-      <c r="D72" s="22" t="n"/>
-      <c r="E72" s="22" t="n"/>
-      <c r="F72" s="22" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr">
-        <is>
-          <t>Interrupt enable register. Selects which raw interrupt events drive the interrupt output.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="38" customHeight="1">
+    <row r="72" ht="195.5" customHeight="1">
+      <c r="A72" s="21" t="n"/>
+      <c r="B72" s="21" t="n"/>
+      <c r="C72" s="21" t="inlineStr">
+        <is>
+          <t>slverr</t>
+        </is>
+      </c>
+      <c r="D72" s="21" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="E72" s="21" t="inlineStr">
+        <is>
+          <t>w1c</t>
+        </is>
+      </c>
+      <c r="F72" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G72" s="21" t="inlineStr">
+        <is>
+          <t>AXI slave error event. Set when a request with an unsupported burst type (FIXED) is answered with SLVERR.
+Usage: details are in hr_err_ri and hr_err_wi; write 1 to clear.
+Values:
+0x0 no event;
+0x1 event occurred.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="195.5" customHeight="1">
       <c r="A73" s="21" t="n"/>
       <c r="B73" s="21" t="n"/>
       <c r="C73" s="21" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>decerr</t>
         </is>
       </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
-          <t>[31:8]</t>
+          <t>[2]</t>
         </is>
       </c>
       <c r="E73" s="21" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>w1c</t>
         </is>
       </c>
       <c r="F73" s="21" t="inlineStr">
@@ -2827,8 +2832,13 @@
       </c>
       <c r="G73" s="21" t="inlineStr">
         <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
+          <t>AXI decode error event. Set when a request addresses bytes outside the aperture and is answered with DECERR.
+Usage: the address and ID of the request are in hr_err_ra and hr_err_wa; write 1 to clear.
+Values:
+0x0 no event;
+0x1 event occurred.
+Unit: none.
+Limits: none.</t>
         </is>
       </c>
     </row>
@@ -2837,17 +2847,17 @@
       <c r="B74" s="21" t="n"/>
       <c r="C74" s="21" t="inlineStr">
         <is>
-          <t>cmd_done</t>
+          <t>cfg_err</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
         <is>
-          <t>[7]</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="E74" s="21" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>w1c</t>
         </is>
       </c>
       <c r="F74" s="21" t="inlineStr">
@@ -2857,32 +2867,32 @@
       </c>
       <c r="G74" s="21" t="inlineStr">
         <is>
-          <t>Device command done interrupt enable. Lets the device command done event of hr_irq_raw drive the interrupt output o_int_hyperram.
-Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
-Values:
-0x0 masked, the event does not raise the interrupt output (reset value);
-0x1 enabled.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="213" customHeight="1">
+          <t>Configuration error event. Set when hr_ctrl.en is written with an illegal field, or when a CSR field is changed in a way that the controller refuses.
+Usage: read hr_sts.cfg_valid to find that a field is illegal; correct the field and write hr_ctrl.en again; write 1 to clear.
+Values:
+0x0 no event;
+0x1 event occurred.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="195.5" customHeight="1">
       <c r="A75" s="21" t="n"/>
       <c r="B75" s="21" t="n"/>
       <c r="C75" s="21" t="inlineStr">
         <is>
-          <t>lat_mis</t>
+          <t>init_ok</t>
         </is>
       </c>
       <c r="D75" s="21" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E75" s="21" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>w1c</t>
         </is>
       </c>
       <c r="F75" s="21" t="inlineStr">
@@ -2892,67 +2902,57 @@
       </c>
       <c r="G75" s="21" t="inlineStr">
         <is>
-          <t>Latency mismatch interrupt enable. Lets the latency mismatch event of hr_irq_raw drive the interrupt output o_int_hyperram.
-Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
-Values:
-0x0 masked, the event does not raise the interrupt output (reset value);
-0x1 enabled.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="213" customHeight="1">
-      <c r="A76" s="21" t="n"/>
-      <c r="B76" s="21" t="n"/>
-      <c r="C76" s="21" t="inlineStr">
-        <is>
-          <t>id_mis</t>
-        </is>
-      </c>
-      <c r="D76" s="21" t="inlineStr">
-        <is>
-          <t>[5]</t>
-        </is>
-      </c>
-      <c r="E76" s="21" t="inlineStr">
-        <is>
-          <t>rw</t>
-        </is>
-      </c>
-      <c r="F76" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G76" s="21" t="inlineStr">
-        <is>
-          <t>ID mismatch interrupt enable. Lets the id mismatch event of hr_irq_raw drive the interrupt output o_int_hyperram.
-Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
-Values:
-0x0 masked, the event does not raise the interrupt output (reset value);
-0x1 enabled.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="213" customHeight="1">
+          <t>Initialization complete event. Set when the start-up sequence has finished.
+Usage: enable it in hr_irq_en to get an interrupt instead of polling hr_sts.init_done; write 1 to clear.
+Values:
+0x0 no event;
+0x1 event occurred.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20.5" customHeight="1">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t>hr_irq_en</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>0x28</t>
+        </is>
+      </c>
+      <c r="C76" s="22" t="n"/>
+      <c r="D76" s="22" t="n"/>
+      <c r="E76" s="22" t="n"/>
+      <c r="F76" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t>Interrupt enable register. Selects which raw interrupt events drive the interrupt output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="38" customHeight="1">
       <c r="A77" s="21" t="n"/>
       <c r="B77" s="21" t="n"/>
       <c r="C77" s="21" t="inlineStr">
         <is>
-          <t>pwr_lost</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="D77" s="21" t="inlineStr">
         <is>
-          <t>[4]</t>
+          <t>[31:9]</t>
         </is>
       </c>
       <c r="E77" s="21" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="F77" s="21" t="inlineStr">
@@ -2962,13 +2962,8 @@
       </c>
       <c r="G77" s="21" t="inlineStr">
         <is>
-          <t>Power loss interrupt enable. Lets the power loss event of hr_irq_raw drive the interrupt output o_int_hyperram.
-Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
-Values:
-0x0 masked, the event does not raise the interrupt output (reset value);
-0x1 enabled.
-Unit: none.
-Limits: none.</t>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
@@ -2977,12 +2972,12 @@
       <c r="B78" s="21" t="n"/>
       <c r="C78" s="21" t="inlineStr">
         <is>
-          <t>slverr</t>
+          <t>tmo</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="E78" s="21" t="inlineStr">
@@ -2997,7 +2992,7 @@
       </c>
       <c r="G78" s="21" t="inlineStr">
         <is>
-          <t>AXI slave error interrupt enable. Lets the axi slave error event of hr_irq_raw drive the interrupt output o_int_hyperram.
+          <t>Device timeout interrupt enable. Lets the device timeout event of hr_irq_raw drive the interrupt output o_int_hyperram.
 Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
 Values:
 0x0 masked, the event does not raise the interrupt output (reset value);
@@ -3012,12 +3007,12 @@
       <c r="B79" s="21" t="n"/>
       <c r="C79" s="21" t="inlineStr">
         <is>
-          <t>decerr</t>
+          <t>cmd_done</t>
         </is>
       </c>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="E79" s="21" t="inlineStr">
@@ -3032,7 +3027,7 @@
       </c>
       <c r="G79" s="21" t="inlineStr">
         <is>
-          <t>AXI decode error interrupt enable. Lets the axi decode error event of hr_irq_raw drive the interrupt output o_int_hyperram.
+          <t>Device command done interrupt enable. Lets the device command done event of hr_irq_raw drive the interrupt output o_int_hyperram.
 Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
 Values:
 0x0 masked, the event does not raise the interrupt output (reset value);
@@ -3047,12 +3042,12 @@
       <c r="B80" s="21" t="n"/>
       <c r="C80" s="21" t="inlineStr">
         <is>
-          <t>cfg_err</t>
+          <t>lat_mis</t>
         </is>
       </c>
       <c r="D80" s="21" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="E80" s="21" t="inlineStr">
@@ -3067,7 +3062,7 @@
       </c>
       <c r="G80" s="21" t="inlineStr">
         <is>
-          <t>Configuration error interrupt enable. Lets the configuration error event of hr_irq_raw drive the interrupt output o_int_hyperram.
+          <t>Latency mismatch interrupt enable. Lets the latency mismatch event of hr_irq_raw drive the interrupt output o_int_hyperram.
 Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
 Values:
 0x0 masked, the event does not raise the interrupt output (reset value);
@@ -3077,17 +3072,17 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="230.5" customHeight="1">
+    <row r="81" ht="213" customHeight="1">
       <c r="A81" s="21" t="n"/>
       <c r="B81" s="21" t="n"/>
       <c r="C81" s="21" t="inlineStr">
         <is>
-          <t>init_ok</t>
+          <t>id_mis</t>
         </is>
       </c>
       <c r="D81" s="21" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="E81" s="21" t="inlineStr">
@@ -3102,7 +3097,7 @@
       </c>
       <c r="G81" s="21" t="inlineStr">
         <is>
-          <t>Initialization complete interrupt enable. Lets the initialization complete event of hr_irq_raw drive the interrupt output o_int_hyperram.
+          <t>ID mismatch interrupt enable. Lets the id mismatch event of hr_irq_raw drive the interrupt output o_int_hyperram.
 Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
 Values:
 0x0 masked, the event does not raise the interrupt output (reset value);
@@ -3112,47 +3107,57 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="20.5" customHeight="1">
-      <c r="A82" s="22" t="inlineStr">
-        <is>
-          <t>hr_irq_sts</t>
-        </is>
-      </c>
-      <c r="B82" s="22" t="inlineStr">
-        <is>
-          <t>0x2C</t>
-        </is>
-      </c>
-      <c r="C82" s="22" t="n"/>
-      <c r="D82" s="22" t="n"/>
-      <c r="E82" s="22" t="n"/>
-      <c r="F82" s="22" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr">
-        <is>
-          <t>Masked interrupt status register. Shows which raw interrupt events are raised and enabled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="38" customHeight="1">
+    <row r="82" ht="213" customHeight="1">
+      <c r="A82" s="21" t="n"/>
+      <c r="B82" s="21" t="n"/>
+      <c r="C82" s="21" t="inlineStr">
+        <is>
+          <t>pwr_lost</t>
+        </is>
+      </c>
+      <c r="D82" s="21" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="E82" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F82" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G82" s="21" t="inlineStr">
+        <is>
+          <t>Power loss interrupt enable. Lets the power loss event of hr_irq_raw drive the interrupt output o_int_hyperram.
+Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
+Values:
+0x0 masked, the event does not raise the interrupt output (reset value);
+0x1 enabled.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="213" customHeight="1">
       <c r="A83" s="21" t="n"/>
       <c r="B83" s="21" t="n"/>
       <c r="C83" s="21" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>slverr</t>
         </is>
       </c>
       <c r="D83" s="21" t="inlineStr">
         <is>
-          <t>[31:8]</t>
+          <t>[3]</t>
         </is>
       </c>
       <c r="E83" s="21" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>rw</t>
         </is>
       </c>
       <c r="F83" s="21" t="inlineStr">
@@ -3162,27 +3167,32 @@
       </c>
       <c r="G83" s="21" t="inlineStr">
         <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="230.5" customHeight="1">
+          <t>AXI slave error interrupt enable. Lets the axi slave error event of hr_irq_raw drive the interrupt output o_int_hyperram.
+Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
+Values:
+0x0 masked, the event does not raise the interrupt output (reset value);
+0x1 enabled.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="213" customHeight="1">
       <c r="A84" s="21" t="n"/>
       <c r="B84" s="21" t="n"/>
       <c r="C84" s="21" t="inlineStr">
         <is>
-          <t>cmd_done</t>
+          <t>decerr</t>
         </is>
       </c>
       <c r="D84" s="21" t="inlineStr">
         <is>
-          <t>[7]</t>
+          <t>[2]</t>
         </is>
       </c>
       <c r="E84" s="21" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>rw</t>
         </is>
       </c>
       <c r="F84" s="21" t="inlineStr">
@@ -3192,32 +3202,32 @@
       </c>
       <c r="G84" s="21" t="inlineStr">
         <is>
-          <t>Device command done masked interrupt status. Reads 1 when the device command done event is raised in hr_irq_raw and enabled in hr_irq_en.
-Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
-Values:
-0x0 not pending (reset value);
-0x1 pending.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="230.5" customHeight="1">
+          <t>AXI decode error interrupt enable. Lets the axi decode error event of hr_irq_raw drive the interrupt output o_int_hyperram.
+Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
+Values:
+0x0 masked, the event does not raise the interrupt output (reset value);
+0x1 enabled.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="213" customHeight="1">
       <c r="A85" s="21" t="n"/>
       <c r="B85" s="21" t="n"/>
       <c r="C85" s="21" t="inlineStr">
         <is>
-          <t>lat_mis</t>
+          <t>cfg_err</t>
         </is>
       </c>
       <c r="D85" s="21" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="E85" s="21" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>rw</t>
         </is>
       </c>
       <c r="F85" s="21" t="inlineStr">
@@ -3227,32 +3237,32 @@
       </c>
       <c r="G85" s="21" t="inlineStr">
         <is>
-          <t>Latency mismatch masked interrupt status. Reads 1 when the latency mismatch event is raised in hr_irq_raw and enabled in hr_irq_en.
-Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
-Values:
-0x0 not pending (reset value);
-0x1 pending.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="213" customHeight="1">
+          <t>Configuration error interrupt enable. Lets the configuration error event of hr_irq_raw drive the interrupt output o_int_hyperram.
+Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
+Values:
+0x0 masked, the event does not raise the interrupt output (reset value);
+0x1 enabled.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="230.5" customHeight="1">
       <c r="A86" s="21" t="n"/>
       <c r="B86" s="21" t="n"/>
       <c r="C86" s="21" t="inlineStr">
         <is>
-          <t>id_mis</t>
+          <t>init_ok</t>
         </is>
       </c>
       <c r="D86" s="21" t="inlineStr">
         <is>
-          <t>[5]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E86" s="21" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>rw</t>
         </is>
       </c>
       <c r="F86" s="21" t="inlineStr">
@@ -3262,62 +3272,52 @@
       </c>
       <c r="G86" s="21" t="inlineStr">
         <is>
-          <t>ID mismatch masked interrupt status. Reads 1 when the id mismatch event is raised in hr_irq_raw and enabled in hr_irq_en.
-Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
-Values:
-0x0 not pending (reset value);
-0x1 pending.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="213" customHeight="1">
-      <c r="A87" s="21" t="n"/>
-      <c r="B87" s="21" t="n"/>
-      <c r="C87" s="21" t="inlineStr">
-        <is>
-          <t>pwr_lost</t>
-        </is>
-      </c>
-      <c r="D87" s="21" t="inlineStr">
-        <is>
-          <t>[4]</t>
-        </is>
-      </c>
-      <c r="E87" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F87" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G87" s="21" t="inlineStr">
-        <is>
-          <t>Power loss masked interrupt status. Reads 1 when the power loss event is raised in hr_irq_raw and enabled in hr_irq_en.
-Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
-Values:
-0x0 not pending (reset value);
-0x1 pending.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="213" customHeight="1">
+          <t>Initialization complete interrupt enable. Lets the initialization complete event of hr_irq_raw drive the interrupt output o_int_hyperram.
+Usage: program it at any time; the interrupt output is the OR of every raw event AND its enable. Clearing the enable does not clear the raw event, it only hides it.
+Values:
+0x0 masked, the event does not raise the interrupt output (reset value);
+0x1 enabled.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20.5" customHeight="1">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>hr_irq_sts</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>0x2C</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="n"/>
+      <c r="D87" s="22" t="n"/>
+      <c r="E87" s="22" t="n"/>
+      <c r="F87" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr">
+        <is>
+          <t>Masked interrupt status register. Shows which raw interrupt events are raised and enabled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="38" customHeight="1">
       <c r="A88" s="21" t="n"/>
       <c r="B88" s="21" t="n"/>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>slverr</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="D88" s="21" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[31:9]</t>
         </is>
       </c>
       <c r="E88" s="21" t="inlineStr">
@@ -3332,27 +3332,22 @@
       </c>
       <c r="G88" s="21" t="inlineStr">
         <is>
-          <t>AXI slave error masked interrupt status. Reads 1 when the axi slave error event is raised in hr_irq_raw and enabled in hr_irq_en.
-Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
-Values:
-0x0 not pending (reset value);
-0x1 pending.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="230.5" customHeight="1">
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="213" customHeight="1">
       <c r="A89" s="21" t="n"/>
       <c r="B89" s="21" t="n"/>
       <c r="C89" s="21" t="inlineStr">
         <is>
-          <t>decerr</t>
+          <t>tmo</t>
         </is>
       </c>
       <c r="D89" s="21" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="E89" s="21" t="inlineStr">
@@ -3367,7 +3362,7 @@
       </c>
       <c r="G89" s="21" t="inlineStr">
         <is>
-          <t>AXI decode error masked interrupt status. Reads 1 when the axi decode error event is raised in hr_irq_raw and enabled in hr_irq_en.
+          <t>Device timeout masked interrupt status. Reads 1 when the device timeout event is raised in hr_irq_raw and enabled in hr_irq_en.
 Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
 Values:
 0x0 not pending (reset value);
@@ -3382,12 +3377,12 @@
       <c r="B90" s="21" t="n"/>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>cfg_err</t>
+          <t>cmd_done</t>
         </is>
       </c>
       <c r="D90" s="21" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="E90" s="21" t="inlineStr">
@@ -3402,7 +3397,7 @@
       </c>
       <c r="G90" s="21" t="inlineStr">
         <is>
-          <t>Configuration error masked interrupt status. Reads 1 when the configuration error event is raised in hr_irq_raw and enabled in hr_irq_en.
+          <t>Device command done masked interrupt status. Reads 1 when the device command done event is raised in hr_irq_raw and enabled in hr_irq_en.
 Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
 Values:
 0x0 not pending (reset value);
@@ -3417,12 +3412,12 @@
       <c r="B91" s="21" t="n"/>
       <c r="C91" s="21" t="inlineStr">
         <is>
-          <t>init_ok</t>
+          <t>lat_mis</t>
         </is>
       </c>
       <c r="D91" s="21" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="E91" s="21" t="inlineStr">
@@ -3437,7 +3432,7 @@
       </c>
       <c r="G91" s="21" t="inlineStr">
         <is>
-          <t>Initialization complete masked interrupt status. Reads 1 when the initialization complete event is raised in hr_irq_raw and enabled in hr_irq_en.
+          <t>Latency mismatch masked interrupt status. Reads 1 when the latency mismatch event is raised in hr_irq_raw and enabled in hr_irq_en.
 Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
 Values:
 0x0 not pending (reset value);
@@ -3447,42 +3442,52 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="20.5" customHeight="1">
-      <c r="A92" s="22" t="inlineStr">
-        <is>
-          <t>hr_irq_inj</t>
-        </is>
-      </c>
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>0x30</t>
-        </is>
-      </c>
-      <c r="C92" s="22" t="n"/>
-      <c r="D92" s="22" t="n"/>
-      <c r="E92" s="22" t="n"/>
-      <c r="F92" s="22" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="G92" s="22" t="inlineStr">
-        <is>
-          <t>Interrupt injection register. Lets software raise raw interrupt events for test.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="38" customHeight="1">
+    <row r="92" ht="213" customHeight="1">
+      <c r="A92" s="21" t="n"/>
+      <c r="B92" s="21" t="n"/>
+      <c r="C92" s="21" t="inlineStr">
+        <is>
+          <t>id_mis</t>
+        </is>
+      </c>
+      <c r="D92" s="21" t="inlineStr">
+        <is>
+          <t>[5]</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F92" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G92" s="21" t="inlineStr">
+        <is>
+          <t>ID mismatch masked interrupt status. Reads 1 when the id mismatch event is raised in hr_irq_raw and enabled in hr_irq_en.
+Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
+Values:
+0x0 not pending (reset value);
+0x1 pending.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="213" customHeight="1">
       <c r="A93" s="21" t="n"/>
       <c r="B93" s="21" t="n"/>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>pwr_lost</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>[31:8]</t>
+          <t>[4]</t>
         </is>
       </c>
       <c r="E93" s="21" t="inlineStr">
@@ -3497,27 +3502,32 @@
       </c>
       <c r="G93" s="21" t="inlineStr">
         <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="230.5" customHeight="1">
+          <t>Power loss masked interrupt status. Reads 1 when the power loss event is raised in hr_irq_raw and enabled in hr_irq_en.
+Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
+Values:
+0x0 not pending (reset value);
+0x1 pending.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="213" customHeight="1">
       <c r="A94" s="21" t="n"/>
       <c r="B94" s="21" t="n"/>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>cmd_done</t>
+          <t>slverr</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>[7]</t>
+          <t>[3]</t>
         </is>
       </c>
       <c r="E94" s="21" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="F94" s="21" t="inlineStr">
@@ -3527,11 +3537,11 @@
       </c>
       <c r="G94" s="21" t="inlineStr">
         <is>
-          <t>Device command done injection. A rising edge from 0 to 1 raises the device command done event of hr_irq_raw once, as if a device register command has completed.
-Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
-Values:
-0x0 no injection (reset value);
-0x1 inject on the rising edge.
+          <t>AXI slave error masked interrupt status. Reads 1 when the axi slave error event is raised in hr_irq_raw and enabled in hr_irq_en.
+Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
+Values:
+0x0 not pending (reset value);
+0x1 pending.
 Unit: none.
 Limits: none.</t>
         </is>
@@ -3542,17 +3552,17 @@
       <c r="B95" s="21" t="n"/>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>lat_mis</t>
+          <t>decerr</t>
         </is>
       </c>
       <c r="D95" s="21" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[2]</t>
         </is>
       </c>
       <c r="E95" s="21" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="F95" s="21" t="inlineStr">
@@ -3562,11 +3572,11 @@
       </c>
       <c r="G95" s="21" t="inlineStr">
         <is>
-          <t>Latency mismatch injection. A rising edge from 0 to 1 raises the latency mismatch event of hr_irq_raw once, as if a device register write changes the CR0 latency code to a value that differs from init_lat.
-Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
-Values:
-0x0 no injection (reset value);
-0x1 inject on the rising edge.
+          <t>AXI decode error masked interrupt status. Reads 1 when the axi decode error event is raised in hr_irq_raw and enabled in hr_irq_en.
+Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
+Values:
+0x0 not pending (reset value);
+0x1 pending.
 Unit: none.
 Limits: none.</t>
         </is>
@@ -3577,17 +3587,17 @@
       <c r="B96" s="21" t="n"/>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>id_mis</t>
+          <t>cfg_err</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
         <is>
-          <t>[5]</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="E96" s="21" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="F96" s="21" t="inlineStr">
@@ -3597,11 +3607,11 @@
       </c>
       <c r="G96" s="21" t="inlineStr">
         <is>
-          <t>ID mismatch injection. A rising edge from 0 to 1 raises the id mismatch event of hr_irq_raw once, as if the ID0 read after start-up differs from the expected value.
-Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
-Values:
-0x0 no injection (reset value);
-0x1 inject on the rising edge.
+          <t>Configuration error masked interrupt status. Reads 1 when the configuration error event is raised in hr_irq_raw and enabled in hr_irq_en.
+Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
+Values:
+0x0 not pending (reset value);
+0x1 pending.
 Unit: none.
 Limits: none.</t>
         </is>
@@ -3612,17 +3622,17 @@
       <c r="B97" s="21" t="n"/>
       <c r="C97" s="21" t="inlineStr">
         <is>
-          <t>pwr_lost</t>
+          <t>init_ok</t>
         </is>
       </c>
       <c r="D97" s="21" t="inlineStr">
         <is>
-          <t>[4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E97" s="21" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="F97" s="21" t="inlineStr">
@@ -3632,67 +3642,57 @@
       </c>
       <c r="G97" s="21" t="inlineStr">
         <is>
-          <t>Power loss injection. A rising edge from 0 to 1 raises the power loss event of hr_irq_raw once, as if the synchronized memory power-good signal falls.
-Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
-Values:
-0x0 no injection (reset value);
-0x1 inject on the rising edge.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="230.5" customHeight="1">
-      <c r="A98" s="21" t="n"/>
-      <c r="B98" s="21" t="n"/>
-      <c r="C98" s="21" t="inlineStr">
-        <is>
-          <t>slverr</t>
-        </is>
-      </c>
-      <c r="D98" s="21" t="inlineStr">
-        <is>
-          <t>[3]</t>
-        </is>
-      </c>
-      <c r="E98" s="21" t="inlineStr">
-        <is>
-          <t>rw</t>
-        </is>
-      </c>
-      <c r="F98" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G98" s="21" t="inlineStr">
-        <is>
-          <t>AXI slave error injection. A rising edge from 0 to 1 raises the axi slave error event of hr_irq_raw once, as if a request is answered with SLVERR.
-Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
-Values:
-0x0 no injection (reset value);
-0x1 inject on the rising edge.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="230.5" customHeight="1">
+          <t>Initialization complete masked interrupt status. Reads 1 when the initialization complete event is raised in hr_irq_raw and enabled in hr_irq_en.
+Usage: read-only; read it in the interrupt handler to find the cause, then clear the cause in hr_irq_raw. The interrupt output is high when any bit is 1.
+Values:
+0x0 not pending (reset value);
+0x1 pending.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20.5" customHeight="1">
+      <c r="A98" s="22" t="inlineStr">
+        <is>
+          <t>hr_irq_inj</t>
+        </is>
+      </c>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>0x30</t>
+        </is>
+      </c>
+      <c r="C98" s="22" t="n"/>
+      <c r="D98" s="22" t="n"/>
+      <c r="E98" s="22" t="n"/>
+      <c r="F98" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr">
+        <is>
+          <t>Interrupt injection register. Lets software raise raw interrupt events for test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="38" customHeight="1">
       <c r="A99" s="21" t="n"/>
       <c r="B99" s="21" t="n"/>
       <c r="C99" s="21" t="inlineStr">
         <is>
-          <t>decerr</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="D99" s="21" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[31:9]</t>
         </is>
       </c>
       <c r="E99" s="21" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="F99" s="21" t="inlineStr">
@@ -3702,13 +3702,8 @@
       </c>
       <c r="G99" s="21" t="inlineStr">
         <is>
-          <t>AXI decode error injection. A rising edge from 0 to 1 raises the axi decode error event of hr_irq_raw once, as if a request is answered with DECERR.
-Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
-Values:
-0x0 no injection (reset value);
-0x1 inject on the rising edge.
-Unit: none.
-Limits: none.</t>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3712,12 @@
       <c r="B100" s="21" t="n"/>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>cfg_err</t>
+          <t>tmo</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="E100" s="21" t="inlineStr">
@@ -3737,7 +3732,7 @@
       </c>
       <c r="G100" s="21" t="inlineStr">
         <is>
-          <t>Configuration error injection. A rising edge from 0 to 1 raises the configuration error event of hr_irq_raw once, as if hr_ctrl.en is written with an illegal field or a preset load is written while enabled.
+          <t>Device timeout injection. A rising edge from 0 to 1 raises the device timeout event of hr_irq_raw once, as if the device did not answer within the programmed wait time.
 Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
 Values:
 0x0 no injection (reset value);
@@ -3752,12 +3747,12 @@
       <c r="B101" s="21" t="n"/>
       <c r="C101" s="21" t="inlineStr">
         <is>
-          <t>init_ok</t>
+          <t>cmd_done</t>
         </is>
       </c>
       <c r="D101" s="21" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="E101" s="21" t="inlineStr">
@@ -3772,7 +3767,7 @@
       </c>
       <c r="G101" s="21" t="inlineStr">
         <is>
-          <t>Initialization complete injection. A rising edge from 0 to 1 raises the initialization complete event of hr_irq_raw once, as if the start-up sequence has finished.
+          <t>Device command done injection. A rising edge from 0 to 1 raises the device command done event of hr_irq_raw once, as if a device register command has completed.
 Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
 Values:
 0x0 no injection (reset value);
@@ -3782,55 +3777,300 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="20.5" customHeight="1">
-      <c r="A102" s="22" t="inlineStr">
-        <is>
-          <t>hr_err_cnt</t>
-        </is>
-      </c>
-      <c r="B102" s="22" t="inlineStr">
-        <is>
-          <t>0x34</t>
-        </is>
-      </c>
-      <c r="C102" s="22" t="n"/>
-      <c r="D102" s="22" t="n"/>
-      <c r="E102" s="22" t="n"/>
-      <c r="F102" s="22" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="G102" s="22" t="inlineStr">
-        <is>
-          <t>AXI error counter register. Counts the AXI requests answered with an error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="178" customHeight="1">
+    <row r="102" ht="230.5" customHeight="1">
+      <c r="A102" s="21" t="n"/>
+      <c r="B102" s="21" t="n"/>
+      <c r="C102" s="21" t="inlineStr">
+        <is>
+          <t>lat_mis</t>
+        </is>
+      </c>
+      <c r="D102" s="21" t="inlineStr">
+        <is>
+          <t>[6]</t>
+        </is>
+      </c>
+      <c r="E102" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F102" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G102" s="21" t="inlineStr">
+        <is>
+          <t>Latency mismatch injection. A rising edge from 0 to 1 raises the latency mismatch event of hr_irq_raw once, as if a device register write changes the CR0 latency code to a value that differs from init_lat.
+Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
+Values:
+0x0 no injection (reset value);
+0x1 inject on the rising edge.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="230.5" customHeight="1">
       <c r="A103" s="21" t="n"/>
       <c r="B103" s="21" t="n"/>
       <c r="C103" s="21" t="inlineStr">
         <is>
+          <t>id_mis</t>
+        </is>
+      </c>
+      <c r="D103" s="21" t="inlineStr">
+        <is>
+          <t>[5]</t>
+        </is>
+      </c>
+      <c r="E103" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G103" s="21" t="inlineStr">
+        <is>
+          <t>ID mismatch injection. A rising edge from 0 to 1 raises the id mismatch event of hr_irq_raw once, as if the ID0 read after start-up differs from the expected value.
+Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
+Values:
+0x0 no injection (reset value);
+0x1 inject on the rising edge.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="230.5" customHeight="1">
+      <c r="A104" s="21" t="n"/>
+      <c r="B104" s="21" t="n"/>
+      <c r="C104" s="21" t="inlineStr">
+        <is>
+          <t>pwr_lost</t>
+        </is>
+      </c>
+      <c r="D104" s="21" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="E104" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F104" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G104" s="21" t="inlineStr">
+        <is>
+          <t>Power loss injection. A rising edge from 0 to 1 raises the power loss event of hr_irq_raw once, as if the synchronized memory power-good signal falls.
+Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
+Values:
+0x0 no injection (reset value);
+0x1 inject on the rising edge.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="230.5" customHeight="1">
+      <c r="A105" s="21" t="n"/>
+      <c r="B105" s="21" t="n"/>
+      <c r="C105" s="21" t="inlineStr">
+        <is>
+          <t>slverr</t>
+        </is>
+      </c>
+      <c r="D105" s="21" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="E105" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G105" s="21" t="inlineStr">
+        <is>
+          <t>AXI slave error injection. A rising edge from 0 to 1 raises the axi slave error event of hr_irq_raw once, as if a request is answered with SLVERR.
+Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
+Values:
+0x0 no injection (reset value);
+0x1 inject on the rising edge.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="230.5" customHeight="1">
+      <c r="A106" s="21" t="n"/>
+      <c r="B106" s="21" t="n"/>
+      <c r="C106" s="21" t="inlineStr">
+        <is>
+          <t>decerr</t>
+        </is>
+      </c>
+      <c r="D106" s="21" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="E106" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F106" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G106" s="21" t="inlineStr">
+        <is>
+          <t>AXI decode error injection. A rising edge from 0 to 1 raises the axi decode error event of hr_irq_raw once, as if a request is answered with DECERR.
+Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
+Values:
+0x0 no injection (reset value);
+0x1 inject on the rising edge.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="230.5" customHeight="1">
+      <c r="A107" s="21" t="n"/>
+      <c r="B107" s="21" t="n"/>
+      <c r="C107" s="21" t="inlineStr">
+        <is>
+          <t>cfg_err</t>
+        </is>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="E107" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G107" s="21" t="inlineStr">
+        <is>
+          <t>Configuration error injection. A rising edge from 0 to 1 raises the configuration error event of hr_irq_raw once, as if hr_ctrl.en is written with an illegal field.
+Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
+Values:
+0x0 no injection (reset value);
+0x1 inject on the rising edge.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="230.5" customHeight="1">
+      <c r="A108" s="21" t="n"/>
+      <c r="B108" s="21" t="n"/>
+      <c r="C108" s="21" t="inlineStr">
+        <is>
+          <t>init_ok</t>
+        </is>
+      </c>
+      <c r="D108" s="21" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E108" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F108" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G108" s="21" t="inlineStr">
+        <is>
+          <t>Initialization complete injection. A rising edge from 0 to 1 raises the initialization complete event of hr_irq_raw once, as if the start-up sequence has finished.
+Usage: write 1 to inject and write 0 before the next injection, because only the rising edge counts; use it with hr_irq_en to test the interrupt path and its handler. The raw event is then cleared in hr_irq_raw as for a real event.
+Values:
+0x0 no injection (reset value);
+0x1 inject on the rising edge.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20.5" customHeight="1">
+      <c r="A109" s="22" t="inlineStr">
+        <is>
+          <t>hr_err_cnt</t>
+        </is>
+      </c>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>0x34</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="n"/>
+      <c r="D109" s="22" t="n"/>
+      <c r="E109" s="22" t="n"/>
+      <c r="F109" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G109" s="22" t="inlineStr">
+        <is>
+          <t>AXI error counter register. Counts the AXI requests answered with an error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="178" customHeight="1">
+      <c r="A110" s="21" t="n"/>
+      <c r="B110" s="21" t="n"/>
+      <c r="C110" s="21" t="inlineStr">
+        <is>
           <t>slverr_cnt</t>
         </is>
       </c>
-      <c r="D103" s="21" t="inlineStr">
+      <c r="D110" s="21" t="inlineStr">
         <is>
           <t>[31:16]</t>
         </is>
       </c>
-      <c r="E103" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F103" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G103" s="21" t="inlineStr">
+      <c r="E110" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F110" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G110" s="21" t="inlineStr">
         <is>
           <t>SLVERR counter. Number of AXI requests answered with SLVERR since the last core reset; saturates at the maximum.
 Usage: read-only; compare with hr_irq_raw.slverr to see repeated errors.
@@ -3841,30 +4081,30 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="178" customHeight="1">
-      <c r="A104" s="21" t="n"/>
-      <c r="B104" s="21" t="n"/>
-      <c r="C104" s="21" t="inlineStr">
+    <row r="111" ht="178" customHeight="1">
+      <c r="A111" s="21" t="n"/>
+      <c r="B111" s="21" t="n"/>
+      <c r="C111" s="21" t="inlineStr">
         <is>
           <t>decerr_cnt</t>
         </is>
       </c>
-      <c r="D104" s="21" t="inlineStr">
+      <c r="D111" s="21" t="inlineStr">
         <is>
           <t>[15:0]</t>
         </is>
       </c>
-      <c r="E104" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F104" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G104" s="21" t="inlineStr">
+      <c r="E111" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F111" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G111" s="21" t="inlineStr">
         <is>
           <t>DECERR counter. Number of AXI requests answered with DECERR since the last core reset; saturates at the maximum.
 Usage: read-only; compare with hr_irq_raw.decerr.
@@ -3875,55 +4115,55 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="20.5" customHeight="1">
-      <c r="A105" s="22" t="inlineStr">
+    <row r="112" ht="20.5" customHeight="1">
+      <c r="A112" s="22" t="inlineStr">
         <is>
           <t>hr_err_ra</t>
         </is>
       </c>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="B112" s="22" t="inlineStr">
         <is>
           <t>0x38</t>
         </is>
       </c>
-      <c r="C105" s="22" t="n"/>
-      <c r="D105" s="22" t="n"/>
-      <c r="E105" s="22" t="n"/>
-      <c r="F105" s="22" t="inlineStr">
+      <c r="C112" s="22" t="n"/>
+      <c r="D112" s="22" t="n"/>
+      <c r="E112" s="22" t="n"/>
+      <c r="F112" s="22" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
-      <c r="G105" s="22" t="inlineStr">
+      <c r="G112" s="22" t="inlineStr">
         <is>
           <t>Last read error address register. Holds the address of the last rejected AXI read.</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="178" customHeight="1">
-      <c r="A106" s="21" t="n"/>
-      <c r="B106" s="21" t="n"/>
-      <c r="C106" s="21" t="inlineStr">
+    <row r="113" ht="178" customHeight="1">
+      <c r="A113" s="21" t="n"/>
+      <c r="B113" s="21" t="n"/>
+      <c r="C113" s="21" t="inlineStr">
         <is>
           <t>addr</t>
         </is>
       </c>
-      <c r="D106" s="21" t="inlineStr">
+      <c r="D113" s="21" t="inlineStr">
         <is>
           <t>[31:0]</t>
         </is>
       </c>
-      <c r="E106" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F106" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G106" s="21" t="inlineStr">
+      <c r="E113" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G113" s="21" t="inlineStr">
         <is>
           <t>Last rejected read address. AXI address of the most recent read that was answered with an error.
 Usage: valid only when the valid bit of hr_err_ri is 1; it is overwritten by the next error.
@@ -3934,290 +4174,72 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="20.5" customHeight="1">
-      <c r="A107" s="22" t="inlineStr">
+    <row r="114" ht="20.5" customHeight="1">
+      <c r="A114" s="22" t="inlineStr">
         <is>
           <t>hr_err_ri</t>
         </is>
       </c>
-      <c r="B107" s="22" t="inlineStr">
+      <c r="B114" s="22" t="inlineStr">
         <is>
           <t>0x3C</t>
         </is>
       </c>
-      <c r="C107" s="22" t="n"/>
-      <c r="D107" s="22" t="n"/>
-      <c r="E107" s="22" t="n"/>
-      <c r="F107" s="22" t="inlineStr">
+      <c r="C114" s="22" t="n"/>
+      <c r="D114" s="22" t="n"/>
+      <c r="E114" s="22" t="n"/>
+      <c r="F114" s="22" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
-      <c r="G107" s="22" t="inlineStr">
+      <c r="G114" s="22" t="inlineStr">
         <is>
           <t>Last read error info register. Holds the ID, the response and the valid flag of the last rejected AXI read.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="38" customHeight="1">
-      <c r="A108" s="21" t="n"/>
-      <c r="B108" s="21" t="n"/>
-      <c r="C108" s="21" t="inlineStr">
+    <row r="115" ht="38" customHeight="1">
+      <c r="A115" s="21" t="n"/>
+      <c r="B115" s="21" t="n"/>
+      <c r="C115" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D108" s="21" t="inlineStr">
+      <c r="D115" s="21" t="inlineStr">
         <is>
           <t>[31:9]</t>
         </is>
       </c>
-      <c r="E108" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F108" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G108" s="21" t="inlineStr">
+      <c r="E115" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F115" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G115" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="195.5" customHeight="1">
-      <c r="A109" s="21" t="n"/>
-      <c r="B109" s="21" t="n"/>
-      <c r="C109" s="21" t="inlineStr">
-        <is>
-          <t>valid</t>
-        </is>
-      </c>
-      <c r="D109" s="21" t="inlineStr">
-        <is>
-          <t>[8]</t>
-        </is>
-      </c>
-      <c r="E109" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F109" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G109" s="21" t="inlineStr">
-        <is>
-          <t>Error info valid. Reads 1 when the address, ID and response registers hold a captured read error.
-Usage: read-only; it stays 1 after the first error until a core reset.
-Values:
-0x0 no error captured;
-0x1 captured.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="38" customHeight="1">
-      <c r="A110" s="21" t="n"/>
-      <c r="B110" s="21" t="n"/>
-      <c r="C110" s="21" t="inlineStr">
-        <is>
-          <t>reserved</t>
-        </is>
-      </c>
-      <c r="D110" s="21" t="inlineStr">
-        <is>
-          <t>[7:6]</t>
-        </is>
-      </c>
-      <c r="E110" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F110" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G110" s="21" t="inlineStr">
-        <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="195.5" customHeight="1">
-      <c r="A111" s="21" t="n"/>
-      <c r="B111" s="21" t="n"/>
-      <c r="C111" s="21" t="inlineStr">
-        <is>
-          <t>resp</t>
-        </is>
-      </c>
-      <c r="D111" s="21" t="inlineStr">
-        <is>
-          <t>[5:4]</t>
-        </is>
-      </c>
-      <c r="E111" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F111" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G111" s="21" t="inlineStr">
-        <is>
-          <t>Last rejected read response. AXI response code returned for the most recent rejected read.
-Usage: valid only when hr_err_ri.valid is 1.
-Values:
-0x2 SLVERR;
-0x3 DECERR.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="178" customHeight="1">
-      <c r="A112" s="21" t="n"/>
-      <c r="B112" s="21" t="n"/>
-      <c r="C112" s="21" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D112" s="21" t="inlineStr">
-        <is>
-          <t>[3:0]</t>
-        </is>
-      </c>
-      <c r="E112" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F112" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G112" s="21" t="inlineStr">
-        <is>
-          <t>Last rejected read ID. AXI ID of the most recent read answered with an error.
-Usage: valid only when hr_err_ri.valid is 1.
-Values:
-0x0 to 0xF AXI ID of the request.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20.5" customHeight="1">
-      <c r="A113" s="22" t="inlineStr">
-        <is>
-          <t>hr_err_wa</t>
-        </is>
-      </c>
-      <c r="B113" s="22" t="inlineStr">
-        <is>
-          <t>0x40</t>
-        </is>
-      </c>
-      <c r="C113" s="22" t="n"/>
-      <c r="D113" s="22" t="n"/>
-      <c r="E113" s="22" t="n"/>
-      <c r="F113" s="22" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="G113" s="22" t="inlineStr">
-        <is>
-          <t>Last write error address register. Holds the address of the last rejected AXI write.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="178" customHeight="1">
-      <c r="A114" s="21" t="n"/>
-      <c r="B114" s="21" t="n"/>
-      <c r="C114" s="21" t="inlineStr">
-        <is>
-          <t>addr</t>
-        </is>
-      </c>
-      <c r="D114" s="21" t="inlineStr">
-        <is>
-          <t>[31:0]</t>
-        </is>
-      </c>
-      <c r="E114" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F114" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G114" s="21" t="inlineStr">
-        <is>
-          <t>Last rejected write address. AXI address of the most recent write that was answered with an error.
-Usage: valid only when the valid bit of hr_err_wi is 1; it is overwritten by the next error.
-Values:
-0x00000000 to 0xFFFFFFFF byte address relative to the aperture window.
-Unit: bytes.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20.5" customHeight="1">
-      <c r="A115" s="22" t="inlineStr">
-        <is>
-          <t>hr_err_wi</t>
-        </is>
-      </c>
-      <c r="B115" s="22" t="inlineStr">
-        <is>
-          <t>0x44</t>
-        </is>
-      </c>
-      <c r="C115" s="22" t="n"/>
-      <c r="D115" s="22" t="n"/>
-      <c r="E115" s="22" t="n"/>
-      <c r="F115" s="22" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="G115" s="22" t="inlineStr">
-        <is>
-          <t>Last write error info register. Holds the ID, the response and the valid flag of the last rejected AXI write.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="38" customHeight="1">
+    <row r="116" ht="195.5" customHeight="1">
       <c r="A116" s="21" t="n"/>
       <c r="B116" s="21" t="n"/>
       <c r="C116" s="21" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>valid</t>
         </is>
       </c>
       <c r="D116" s="21" t="inlineStr">
         <is>
-          <t>[31:9]</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="E116" s="21" t="inlineStr">
@@ -4232,22 +4254,27 @@
       </c>
       <c r="G116" s="21" t="inlineStr">
         <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="195.5" customHeight="1">
+          <t>Error info valid. Reads 1 when the address, ID and response registers hold a captured read error.
+Usage: read-only; it stays 1 after the first error until a core reset.
+Values:
+0x0 no error captured;
+0x1 captured.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="38" customHeight="1">
       <c r="A117" s="21" t="n"/>
       <c r="B117" s="21" t="n"/>
       <c r="C117" s="21" t="inlineStr">
         <is>
-          <t>valid</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="D117" s="21" t="inlineStr">
         <is>
-          <t>[8]</t>
+          <t>[7:6]</t>
         </is>
       </c>
       <c r="E117" s="21" t="inlineStr">
@@ -4262,27 +4289,22 @@
       </c>
       <c r="G117" s="21" t="inlineStr">
         <is>
-          <t>Error info valid. Reads 1 when the address, ID and response registers hold a captured write error.
-Usage: read-only; it stays 1 after the first error until a core reset.
-Values:
-0x0 no error captured;
-0x1 captured.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="38" customHeight="1">
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="195.5" customHeight="1">
       <c r="A118" s="21" t="n"/>
       <c r="B118" s="21" t="n"/>
       <c r="C118" s="21" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>resp</t>
         </is>
       </c>
       <c r="D118" s="21" t="inlineStr">
         <is>
-          <t>[7:6]</t>
+          <t>[5:4]</t>
         </is>
       </c>
       <c r="E118" s="21" t="inlineStr">
@@ -4297,22 +4319,27 @@
       </c>
       <c r="G118" s="21" t="inlineStr">
         <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="195.5" customHeight="1">
+          <t>Last rejected read response. AXI response code returned for the most recent rejected read.
+Usage: valid only when hr_err_ri.valid is 1.
+Values:
+0x2 SLVERR;
+0x3 DECERR.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="178" customHeight="1">
       <c r="A119" s="21" t="n"/>
       <c r="B119" s="21" t="n"/>
       <c r="C119" s="21" t="inlineStr">
         <is>
-          <t>resp</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D119" s="21" t="inlineStr">
         <is>
-          <t>[5:4]</t>
+          <t>[3:0]</t>
         </is>
       </c>
       <c r="E119" s="21" t="inlineStr">
@@ -4327,43 +4354,8 @@
       </c>
       <c r="G119" s="21" t="inlineStr">
         <is>
-          <t>Last rejected write response. AXI response code returned for the most recent rejected write.
-Usage: valid only when hr_err_wi.valid is 1.
-Values:
-0x2 SLVERR;
-0x3 DECERR.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="178" customHeight="1">
-      <c r="A120" s="21" t="n"/>
-      <c r="B120" s="21" t="n"/>
-      <c r="C120" s="21" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D120" s="21" t="inlineStr">
-        <is>
-          <t>[3:0]</t>
-        </is>
-      </c>
-      <c r="E120" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F120" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G120" s="21" t="inlineStr">
-        <is>
-          <t>Last rejected write ID. AXI ID of the most recent write answered with an error.
-Usage: valid only when hr_err_wi.valid is 1.
+          <t>Last rejected read ID. AXI ID of the most recent read answered with an error.
+Usage: valid only when hr_err_ri.valid is 1.
 Values:
 0x0 to 0xF AXI ID of the request.
 Unit: none.
@@ -4371,85 +4363,666 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="20.5" customHeight="1">
-      <c r="A121" s="22" t="inlineStr">
-        <is>
-          <t>hr_d0_cfg</t>
-        </is>
-      </c>
-      <c r="B121" s="22" t="inlineStr">
-        <is>
-          <t>0x100</t>
-        </is>
-      </c>
-      <c r="C121" s="22" t="n"/>
-      <c r="D121" s="22" t="n"/>
-      <c r="E121" s="22" t="n"/>
-      <c r="F121" s="22" t="inlineStr">
-        <is>
-          <t>0x0001C4E0</t>
-        </is>
-      </c>
-      <c r="G121" s="22" t="inlineStr">
-        <is>
-          <t>Chip select 0 device configuration register. Selects the device preset and the latency and mode values written to the device.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="38" customHeight="1">
-      <c r="A122" s="21" t="n"/>
-      <c r="B122" s="21" t="n"/>
-      <c r="C122" s="21" t="inlineStr">
-        <is>
-          <t>reserved</t>
-        </is>
-      </c>
-      <c r="D122" s="21" t="inlineStr">
-        <is>
-          <t>[31:20]</t>
-        </is>
-      </c>
-      <c r="E122" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F122" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G122" s="21" t="inlineStr">
-        <is>
-          <t>This field is unused.
-Read-as-zero and write-ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="195.5" customHeight="1">
+    <row r="120" ht="20.5" customHeight="1">
+      <c r="A120" s="22" t="inlineStr">
+        <is>
+          <t>hr_err_wa</t>
+        </is>
+      </c>
+      <c r="B120" s="22" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="C120" s="22" t="n"/>
+      <c r="D120" s="22" t="n"/>
+      <c r="E120" s="22" t="n"/>
+      <c r="F120" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G120" s="22" t="inlineStr">
+        <is>
+          <t>Last write error address register. Holds the address of the last rejected AXI write.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="178" customHeight="1">
+      <c r="A121" s="21" t="n"/>
+      <c r="B121" s="21" t="n"/>
+      <c r="C121" s="21" t="inlineStr">
+        <is>
+          <t>addr</t>
+        </is>
+      </c>
+      <c r="D121" s="21" t="inlineStr">
+        <is>
+          <t>[31:0]</t>
+        </is>
+      </c>
+      <c r="E121" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G121" s="21" t="inlineStr">
+        <is>
+          <t>Last rejected write address. AXI address of the most recent write that was answered with an error.
+Usage: valid only when the valid bit of hr_err_wi is 1; it is overwritten by the next error.
+Values:
+0x00000000 to 0xFFFFFFFF byte address relative to the aperture window.
+Unit: bytes.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20.5" customHeight="1">
+      <c r="A122" s="22" t="inlineStr">
+        <is>
+          <t>hr_err_wi</t>
+        </is>
+      </c>
+      <c r="B122" s="22" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="C122" s="22" t="n"/>
+      <c r="D122" s="22" t="n"/>
+      <c r="E122" s="22" t="n"/>
+      <c r="F122" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G122" s="22" t="inlineStr">
+        <is>
+          <t>Last write error info register. Holds the ID, the response and the valid flag of the last rejected AXI write.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="38" customHeight="1">
       <c r="A123" s="21" t="n"/>
       <c r="B123" s="21" t="n"/>
       <c r="C123" s="21" t="inlineStr">
         <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D123" s="21" t="inlineStr">
+        <is>
+          <t>[31:9]</t>
+        </is>
+      </c>
+      <c r="E123" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G123" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="195.5" customHeight="1">
+      <c r="A124" s="21" t="n"/>
+      <c r="B124" s="21" t="n"/>
+      <c r="C124" s="21" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="D124" s="21" t="inlineStr">
+        <is>
+          <t>[8]</t>
+        </is>
+      </c>
+      <c r="E124" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F124" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G124" s="21" t="inlineStr">
+        <is>
+          <t>Error info valid. Reads 1 when the address, ID and response registers hold a captured write error.
+Usage: read-only; it stays 1 after the first error until a core reset.
+Values:
+0x0 no error captured;
+0x1 captured.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="38" customHeight="1">
+      <c r="A125" s="21" t="n"/>
+      <c r="B125" s="21" t="n"/>
+      <c r="C125" s="21" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D125" s="21" t="inlineStr">
+        <is>
+          <t>[7:6]</t>
+        </is>
+      </c>
+      <c r="E125" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G125" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="195.5" customHeight="1">
+      <c r="A126" s="21" t="n"/>
+      <c r="B126" s="21" t="n"/>
+      <c r="C126" s="21" t="inlineStr">
+        <is>
+          <t>resp</t>
+        </is>
+      </c>
+      <c r="D126" s="21" t="inlineStr">
+        <is>
+          <t>[5:4]</t>
+        </is>
+      </c>
+      <c r="E126" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F126" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G126" s="21" t="inlineStr">
+        <is>
+          <t>Last rejected write response. AXI response code returned for the most recent rejected write.
+Usage: valid only when hr_err_wi.valid is 1.
+Values:
+0x2 SLVERR;
+0x3 DECERR.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="178" customHeight="1">
+      <c r="A127" s="21" t="n"/>
+      <c r="B127" s="21" t="n"/>
+      <c r="C127" s="21" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D127" s="21" t="inlineStr">
+        <is>
+          <t>[3:0]</t>
+        </is>
+      </c>
+      <c r="E127" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G127" s="21" t="inlineStr">
+        <is>
+          <t>Last rejected write ID. AXI ID of the most recent write answered with an error.
+Usage: valid only when hr_err_wi.valid is 1.
+Values:
+0x0 to 0xF AXI ID of the request.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20.5" customHeight="1">
+      <c r="A128" s="22" t="inlineStr">
+        <is>
+          <t>hr_tmo_log</t>
+        </is>
+      </c>
+      <c r="B128" s="22" t="inlineStr">
+        <is>
+          <t>0x48</t>
+        </is>
+      </c>
+      <c r="C128" s="22" t="n"/>
+      <c r="D128" s="22" t="n"/>
+      <c r="E128" s="22" t="n"/>
+      <c r="F128" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G128" s="22" t="inlineStr">
+        <is>
+          <t>Timeout log register. Holds what the controller was doing and waiting for when the last device timeout happened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="38" customHeight="1">
+      <c r="A129" s="21" t="n"/>
+      <c r="B129" s="21" t="n"/>
+      <c r="C129" s="21" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D129" s="21" t="inlineStr">
+        <is>
+          <t>[31:24]</t>
+        </is>
+      </c>
+      <c r="E129" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G129" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="265.5" customHeight="1">
+      <c r="A130" s="21" t="n"/>
+      <c r="B130" s="21" t="n"/>
+      <c r="C130" s="21" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="D130" s="21" t="inlineStr">
+        <is>
+          <t>[23:20]</t>
+        </is>
+      </c>
+      <c r="E130" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F130" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G130" s="21" t="inlineStr">
+        <is>
+          <t>Waited-for event. The step that the controller was waiting for when the time ran out.
+Usage: read-only; valid only while valid = 1; together with cmd it tells whether the device or the AXI side was late.
+Values:
+0x0 none;
+0x1 RWDS level in the command phase;
+0x2 first read data strobe edge after the latency;
+0x3 next read data strobe edge in a burst;
+0x4 capture FIFO data;
+0x5 to 0xF reserved.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="300.5" customHeight="1">
+      <c r="A131" s="21" t="n"/>
+      <c r="B131" s="21" t="n"/>
+      <c r="C131" s="21" t="inlineStr">
+        <is>
+          <t>cmd</t>
+        </is>
+      </c>
+      <c r="D131" s="21" t="inlineStr">
+        <is>
+          <t>[19:16]</t>
+        </is>
+      </c>
+      <c r="E131" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G131" s="21" t="inlineStr">
+        <is>
+          <t>Command in progress. The kind of command that the controller was executing.
+Usage: read-only; valid only while valid = 1.
+Values:
+0x0 none;
+0x1 start-up register write;
+0x2 start-up ID0 read;
+0x3 memory read;
+0x4 memory write;
+0x5 device register read;
+0x6 device register write;
+0x7 to 0xF reserved.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="178" customHeight="1">
+      <c r="A132" s="21" t="n"/>
+      <c r="B132" s="21" t="n"/>
+      <c r="C132" s="21" t="inlineStr">
+        <is>
+          <t>beats</t>
+        </is>
+      </c>
+      <c r="D132" s="21" t="inlineStr">
+        <is>
+          <t>[15:3]</t>
+        </is>
+      </c>
+      <c r="E132" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F132" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G132" s="21" t="inlineStr">
+        <is>
+          <t>Completed words. Number of 16-bit words transferred in the failed transaction before the timeout.
+Usage: read-only; valid only while valid = 1; with hr_tmo_addr it gives the failing position inside a burst.
+Values:
+0x0000 to 0x1FFF number of completed 16-bit words, saturating.
+Unit: 16-bit words.
+Limits: counts up to 8191.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="195.5" customHeight="1">
+      <c r="A133" s="21" t="n"/>
+      <c r="B133" s="21" t="n"/>
+      <c r="C133" s="21" t="inlineStr">
+        <is>
+          <t>wr</t>
+        </is>
+      </c>
+      <c r="D133" s="21" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="E133" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F133" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G133" s="21" t="inlineStr">
+        <is>
+          <t>Timed-out direction. Direction of the command that timed out.
+Usage: read-only; valid only while valid = 1.
+Values:
+0x0 read;
+0x1 write.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="195.5" customHeight="1">
+      <c r="A134" s="21" t="n"/>
+      <c r="B134" s="21" t="n"/>
+      <c r="C134" s="21" t="inlineStr">
+        <is>
+          <t>cs</t>
+        </is>
+      </c>
+      <c r="D134" s="21" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="E134" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F134" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G134" s="21" t="inlineStr">
+        <is>
+          <t>Timed-out chip select. The chip select (device) that did not answer.
+Usage: read-only; valid only while valid = 1.
+Values:
+0x0 chip select 0;
+0x1 chip select 1.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="230.5" customHeight="1">
+      <c r="A135" s="21" t="n"/>
+      <c r="B135" s="21" t="n"/>
+      <c r="C135" s="21" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="D135" s="21" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E135" s="21" t="inlineStr">
+        <is>
+          <t>w1c</t>
+        </is>
+      </c>
+      <c r="F135" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G135" s="21" t="inlineStr">
+        <is>
+          <t>Log valid flag. Hardware sets it with the first timeout and the log registers then keep their values; software clears it to arm the next capture.
+Usage: read the log (hr_tmo_log and hr_tmo_addr) after hr_irq_raw.tmo is set, then write 1 here. A second timeout while it is 1 does not overwrite the log. A hardware set in the same cycle as the clear wins.
+Values:
+0x0 no log captured (reset value);
+0x1 log captured.
+Unit: none.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20.5" customHeight="1">
+      <c r="A136" s="22" t="inlineStr">
+        <is>
+          <t>hr_tmo_addr</t>
+        </is>
+      </c>
+      <c r="B136" s="22" t="inlineStr">
+        <is>
+          <t>0x4C</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="n"/>
+      <c r="D136" s="22" t="n"/>
+      <c r="E136" s="22" t="n"/>
+      <c r="F136" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G136" s="22" t="inlineStr">
+        <is>
+          <t>Timeout address register. Holds the address of the transaction that timed out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="195.5" customHeight="1">
+      <c r="A137" s="21" t="n"/>
+      <c r="B137" s="21" t="n"/>
+      <c r="C137" s="21" t="inlineStr">
+        <is>
+          <t>addr</t>
+        </is>
+      </c>
+      <c r="D137" s="21" t="inlineStr">
+        <is>
+          <t>[31:0]</t>
+        </is>
+      </c>
+      <c r="E137" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F137" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G137" s="21" t="inlineStr">
+        <is>
+          <t>Timed-out address. Byte address, relative to the aperture window, of the first byte of the transaction that timed out; for a device register command it is the register word address.
+Usage: read-only; valid only while hr_tmo_log.valid = 1.
+Values:
+0x00000000 to 0xFFFFFFFF byte address relative to the aperture window.
+Unit: bytes.
+Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20.5" customHeight="1">
+      <c r="A138" s="22" t="inlineStr">
+        <is>
+          <t>hr_d0_cfg</t>
+        </is>
+      </c>
+      <c r="B138" s="22" t="inlineStr">
+        <is>
+          <t>0x100</t>
+        </is>
+      </c>
+      <c r="C138" s="22" t="n"/>
+      <c r="D138" s="22" t="n"/>
+      <c r="E138" s="22" t="n"/>
+      <c r="F138" s="22" t="inlineStr">
+        <is>
+          <t>0x0001C4E0</t>
+        </is>
+      </c>
+      <c r="G138" s="22" t="inlineStr">
+        <is>
+          <t>Chip select 0 device configuration register. Holds the latency and mode values written to the device.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="38" customHeight="1">
+      <c r="A139" s="21" t="n"/>
+      <c r="B139" s="21" t="n"/>
+      <c r="C139" s="21" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D139" s="21" t="inlineStr">
+        <is>
+          <t>[31:20]</t>
+        </is>
+      </c>
+      <c r="E139" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F139" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G139" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="195.5" customHeight="1">
+      <c r="A140" s="21" t="n"/>
+      <c r="B140" s="21" t="n"/>
+      <c r="C140" s="21" t="inlineStr">
+        <is>
           <t>pasr</t>
         </is>
       </c>
-      <c r="D123" s="21" t="inlineStr">
+      <c r="D140" s="21" t="inlineStr">
         <is>
           <t>[19:17]</t>
         </is>
       </c>
-      <c r="E123" s="21" t="inlineStr">
+      <c r="E140" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F123" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G123" s="21" t="inlineStr">
+      <c r="F140" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G140" s="21" t="inlineStr">
         <is>
           <t>Partial array refresh code. Value written into CR1[4:2] to choose which part of the array is refreshed.
 Usage: program it while hr_ctrl.en = 0; the data outside the refreshed part is lost.
@@ -4461,30 +5034,30 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="248" customHeight="1">
-      <c r="A124" s="21" t="n"/>
-      <c r="B124" s="21" t="n"/>
-      <c r="C124" s="21" t="inlineStr">
+    <row r="141" ht="248" customHeight="1">
+      <c r="A141" s="21" t="n"/>
+      <c r="B141" s="21" t="n"/>
+      <c r="C141" s="21" t="inlineStr">
         <is>
           <t>blen</t>
         </is>
       </c>
-      <c r="D124" s="21" t="inlineStr">
+      <c r="D141" s="21" t="inlineStr">
         <is>
           <t>[16:15]</t>
         </is>
       </c>
-      <c r="E124" s="21" t="inlineStr">
+      <c r="E141" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F124" s="21" t="inlineStr">
+      <c r="F141" s="21" t="inlineStr">
         <is>
           <t>0x3</t>
         </is>
       </c>
-      <c r="G124" s="21" t="inlineStr">
+      <c r="G141" s="21" t="inlineStr">
         <is>
           <t>Wrapped burst group size. Value written into CR0[1:0]; an AXI WRAP burst of the same byte length is sent as one wrapped HyperBus burst, others are split into two linear bursts.
 Usage: program it while hr_ctrl.en = 0; choose the cache line size of the system for critical-word-first reads.
@@ -4498,30 +5071,30 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="195.5" customHeight="1">
-      <c r="A125" s="21" t="n"/>
-      <c r="B125" s="21" t="n"/>
-      <c r="C125" s="21" t="inlineStr">
+    <row r="142" ht="195.5" customHeight="1">
+      <c r="A142" s="21" t="n"/>
+      <c r="B142" s="21" t="n"/>
+      <c r="C142" s="21" t="inlineStr">
         <is>
           <t>hybrid</t>
         </is>
       </c>
-      <c r="D125" s="21" t="inlineStr">
+      <c r="D142" s="21" t="inlineStr">
         <is>
           <t>[14]</t>
         </is>
       </c>
-      <c r="E125" s="21" t="inlineStr">
+      <c r="E142" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F125" s="21" t="inlineStr">
+      <c r="F142" s="21" t="inlineStr">
         <is>
           <t>0x1</t>
         </is>
       </c>
-      <c r="G125" s="21" t="inlineStr">
+      <c r="G142" s="21" t="inlineStr">
         <is>
           <t>Hybrid burst control. Value written into CR0[2], which selects how a wrapped burst continues after the wrap group.
 Usage: program it while hr_ctrl.en = 0; it matters only for wrapped bursts of the devices that support hybrid burst.
@@ -4533,30 +5106,30 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="178" customHeight="1">
-      <c r="A126" s="21" t="n"/>
-      <c r="B126" s="21" t="n"/>
-      <c r="C126" s="21" t="inlineStr">
+    <row r="143" ht="178" customHeight="1">
+      <c r="A143" s="21" t="n"/>
+      <c r="B143" s="21" t="n"/>
+      <c r="C143" s="21" t="inlineStr">
         <is>
           <t>drive</t>
         </is>
       </c>
-      <c r="D126" s="21" t="inlineStr">
+      <c r="D143" s="21" t="inlineStr">
         <is>
           <t>[13:11]</t>
         </is>
       </c>
-      <c r="E126" s="21" t="inlineStr">
+      <c r="E143" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F126" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G126" s="21" t="inlineStr">
+      <c r="F143" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G143" s="21" t="inlineStr">
         <is>
           <t>Output drive strength code. Value written into CR0[14:12] to set the output impedance of the DQ and RWDS drivers of the device.
 Usage: program it while hr_ctrl.en = 0; choose it for the board; the code meaning is given in the device datasheet.
@@ -4567,30 +5140,30 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="230.5" customHeight="1">
-      <c r="A127" s="21" t="n"/>
-      <c r="B127" s="21" t="n"/>
-      <c r="C127" s="21" t="inlineStr">
+    <row r="144" ht="230.5" customHeight="1">
+      <c r="A144" s="21" t="n"/>
+      <c r="B144" s="21" t="n"/>
+      <c r="C144" s="21" t="inlineStr">
         <is>
           <t>fixed_lat</t>
         </is>
       </c>
-      <c r="D127" s="21" t="inlineStr">
+      <c r="D144" s="21" t="inlineStr">
         <is>
           <t>[10]</t>
         </is>
       </c>
-      <c r="E127" s="21" t="inlineStr">
+      <c r="E144" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F127" s="21" t="inlineStr">
+      <c r="F144" s="21" t="inlineStr">
         <is>
           <t>0x1</t>
         </is>
       </c>
-      <c r="G127" s="21" t="inlineStr">
+      <c r="G144" s="21" t="inlineStr">
         <is>
           <t>Fixed latency enable. Selects whether the latency is always twice the initial latency or follows RWDS in the command and address phase; written into CR0[3].
 Usage: program it while hr_ctrl.en = 0 together with init_lat. In variable mode the controller samples RWDS during the CA phase and waits 1x or 2x init_lat.
@@ -4602,30 +5175,30 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="230.5" customHeight="1">
-      <c r="A128" s="21" t="n"/>
-      <c r="B128" s="21" t="n"/>
-      <c r="C128" s="21" t="inlineStr">
+    <row r="145" ht="230.5" customHeight="1">
+      <c r="A145" s="21" t="n"/>
+      <c r="B145" s="21" t="n"/>
+      <c r="C145" s="21" t="inlineStr">
         <is>
           <t>init_lat</t>
         </is>
       </c>
-      <c r="D128" s="21" t="inlineStr">
+      <c r="D145" s="21" t="inlineStr">
         <is>
           <t>[9:5]</t>
         </is>
       </c>
-      <c r="E128" s="21" t="inlineStr">
+      <c r="E145" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F128" s="21" t="inlineStr">
+      <c r="F145" s="21" t="inlineStr">
         <is>
           <t>0x7</t>
         </is>
       </c>
-      <c r="G128" s="21" t="inlineStr">
+      <c r="G145" s="21" t="inlineStr">
         <is>
           <t>Initial latency. Number of CK periods the controller waits between the command and address phase and the first data; the controller encodes it into CR0[7:4] at start-up.
 Usage: program it while hr_ctrl.en = 0; with fixed latency the wait is twice this value. Keep it equal to the latency code in the device CR0, otherwise hr_irq_raw.lat_mis is set when CR0 is changed by software.
@@ -4637,130 +5210,85 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="230.5" customHeight="1">
-      <c r="A129" s="21" t="n"/>
-      <c r="B129" s="21" t="n"/>
-      <c r="C129" s="21" t="inlineStr">
-        <is>
-          <t>preset_go</t>
-        </is>
-      </c>
-      <c r="D129" s="21" t="inlineStr">
-        <is>
-          <t>[4]</t>
-        </is>
-      </c>
-      <c r="E129" s="21" t="inlineStr">
-        <is>
-          <t>rwi</t>
-        </is>
-      </c>
-      <c r="F129" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G129" s="21" t="inlineStr">
-        <is>
-          <t>Preset load command. Writing 1 copies the timing, latency and ID fields of the selected preset into the register group of chip select 0; hardware clears it when done.
-Usage: write 1 only while hr_ctrl.en = 0, after writing preset; a write while enabled is ignored and sets hr_irq_raw.cfg_err. A software write wins over the hardware clear in the same cycle.
-Values:
-0x0 no load (reset value);
-0x1 load the preset; reads 0x1 until the load is done.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="318" customHeight="1">
-      <c r="A130" s="21" t="n"/>
-      <c r="B130" s="21" t="n"/>
-      <c r="C130" s="21" t="inlineStr">
-        <is>
-          <t>preset</t>
-        </is>
-      </c>
-      <c r="D130" s="21" t="inlineStr">
-        <is>
-          <t>[3:0]</t>
-        </is>
-      </c>
-      <c r="E130" s="21" t="inlineStr">
+    <row r="146" ht="38" customHeight="1">
+      <c r="A146" s="21" t="n"/>
+      <c r="B146" s="21" t="n"/>
+      <c r="C146" s="21" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D146" s="21" t="inlineStr">
+        <is>
+          <t>[4:0]</t>
+        </is>
+      </c>
+      <c r="E146" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F146" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G146" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20.5" customHeight="1">
+      <c r="A147" s="22" t="inlineStr">
+        <is>
+          <t>hr_d0_trst</t>
+        </is>
+      </c>
+      <c r="B147" s="22" t="inlineStr">
+        <is>
+          <t>0x104</t>
+        </is>
+      </c>
+      <c r="C147" s="22" t="n"/>
+      <c r="D147" s="22" t="n"/>
+      <c r="E147" s="22" t="n"/>
+      <c r="F147" s="22" t="inlineStr">
+        <is>
+          <t>0x00500050</t>
+        </is>
+      </c>
+      <c r="G147" s="22" t="inlineStr">
+        <is>
+          <t>Chip select 0 RESET# timing register. Sets the RESET# low time and the wait after RESET# is released.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="195.5" customHeight="1">
+      <c r="A148" s="21" t="n"/>
+      <c r="B148" s="21" t="n"/>
+      <c r="C148" s="21" t="inlineStr">
+        <is>
+          <t>t_rh</t>
+        </is>
+      </c>
+      <c r="D148" s="21" t="inlineStr">
+        <is>
+          <t>[31:16]</t>
+        </is>
+      </c>
+      <c r="E148" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F130" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G130" s="21" t="inlineStr">
-        <is>
-          <t>Device preset select. Chooses the set of default timing values of one target device that the load command copies into the register group of chip select 0.
-Usage: write it, then write preset_go = 1, while hr_ctrl.en = 0; you may overwrite any field afterwards. The loaded values are listed in the specification.
-Values:
-0x0 safe values for all target devices (reset value);
-0x1 S80KS2562;
-0x2 W958D8NBYA;
-0x3 IS66WVH32M8DALL;
-0x4 S80KS2564;
-0x5 W958D6NBKX;
-0x6 to 0xF reserved.
-Unit: none.
-Limits: do not write 0x6 to 0xF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20.5" customHeight="1">
-      <c r="A131" s="22" t="inlineStr">
-        <is>
-          <t>hr_d0_trst</t>
-        </is>
-      </c>
-      <c r="B131" s="22" t="inlineStr">
-        <is>
-          <t>0x104</t>
-        </is>
-      </c>
-      <c r="C131" s="22" t="n"/>
-      <c r="D131" s="22" t="n"/>
-      <c r="E131" s="22" t="n"/>
-      <c r="F131" s="22" t="inlineStr">
-        <is>
-          <t>0x00500050</t>
-        </is>
-      </c>
-      <c r="G131" s="22" t="inlineStr">
-        <is>
-          <t>Chip select 0 RESET# timing register. Sets the RESET# low time and the wait after RESET# is released.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="195.5" customHeight="1">
-      <c r="A132" s="21" t="n"/>
-      <c r="B132" s="21" t="n"/>
-      <c r="C132" s="21" t="inlineStr">
-        <is>
-          <t>t_rh</t>
-        </is>
-      </c>
-      <c r="D132" s="21" t="inlineStr">
-        <is>
-          <t>[31:16]</t>
-        </is>
-      </c>
-      <c r="E132" s="21" t="inlineStr">
-        <is>
-          <t>rw</t>
-        </is>
-      </c>
-      <c r="F132" s="21" t="inlineStr">
+      <c r="F148" s="21" t="inlineStr">
         <is>
           <t>0x50</t>
         </is>
       </c>
-      <c r="G132" s="21" t="inlineStr">
+      <c r="G148" s="21" t="inlineStr">
         <is>
           <t>RESET# high to CS# low time. Number of CK periods the controller waits after RESET# is released before CS# may go low.
 Usage: program it while hr_ctrl.en = 0; it must cover the device tRH (200 ns on the target devices).
@@ -4772,30 +5300,30 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="213" customHeight="1">
-      <c r="A133" s="21" t="n"/>
-      <c r="B133" s="21" t="n"/>
-      <c r="C133" s="21" t="inlineStr">
+    <row r="149" ht="213" customHeight="1">
+      <c r="A149" s="21" t="n"/>
+      <c r="B149" s="21" t="n"/>
+      <c r="C149" s="21" t="inlineStr">
         <is>
           <t>t_rp</t>
         </is>
       </c>
-      <c r="D133" s="21" t="inlineStr">
+      <c r="D149" s="21" t="inlineStr">
         <is>
           <t>[15:0]</t>
         </is>
       </c>
-      <c r="E133" s="21" t="inlineStr">
+      <c r="E149" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F133" s="21" t="inlineStr">
+      <c r="F149" s="21" t="inlineStr">
         <is>
           <t>0x50</t>
         </is>
       </c>
-      <c r="G133" s="21" t="inlineStr">
+      <c r="G149" s="21" t="inlineStr">
         <is>
           <t>RESET# pulse width. Number of CK periods the controller holds RESET# low at start-up.
 Usage: program it while hr_ctrl.en = 0; with two chip selects the larger value of both groups is used; it must cover the device tRP (200 ns on the target devices).
@@ -4807,85 +5335,85 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="20.5" customHeight="1">
-      <c r="A134" s="22" t="inlineStr">
+    <row r="150" ht="20.5" customHeight="1">
+      <c r="A150" s="22" t="inlineStr">
         <is>
           <t>hr_d0_trph</t>
         </is>
       </c>
-      <c r="B134" s="22" t="inlineStr">
+      <c r="B150" s="22" t="inlineStr">
         <is>
           <t>0x108</t>
         </is>
       </c>
-      <c r="C134" s="22" t="n"/>
-      <c r="D134" s="22" t="n"/>
-      <c r="E134" s="22" t="n"/>
-      <c r="F134" s="22" t="inlineStr">
+      <c r="C150" s="22" t="n"/>
+      <c r="D150" s="22" t="n"/>
+      <c r="E150" s="22" t="n"/>
+      <c r="F150" s="22" t="inlineStr">
         <is>
           <t>0x000000A0</t>
         </is>
       </c>
-      <c r="G134" s="22" t="inlineStr">
+      <c r="G150" s="22" t="inlineStr">
         <is>
           <t>Chip select 0 RESET# low to CS# low register. Sets the wait from the start of RESET# to the first access.</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="38" customHeight="1">
-      <c r="A135" s="21" t="n"/>
-      <c r="B135" s="21" t="n"/>
-      <c r="C135" s="21" t="inlineStr">
+    <row r="151" ht="38" customHeight="1">
+      <c r="A151" s="21" t="n"/>
+      <c r="B151" s="21" t="n"/>
+      <c r="C151" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D135" s="21" t="inlineStr">
+      <c r="D151" s="21" t="inlineStr">
         <is>
           <t>[31:16]</t>
         </is>
       </c>
-      <c r="E135" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F135" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G135" s="21" t="inlineStr">
+      <c r="E151" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F151" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G151" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="195.5" customHeight="1">
-      <c r="A136" s="21" t="n"/>
-      <c r="B136" s="21" t="n"/>
-      <c r="C136" s="21" t="inlineStr">
+    <row r="152" ht="195.5" customHeight="1">
+      <c r="A152" s="21" t="n"/>
+      <c r="B152" s="21" t="n"/>
+      <c r="C152" s="21" t="inlineStr">
         <is>
           <t>t_rph</t>
         </is>
       </c>
-      <c r="D136" s="21" t="inlineStr">
+      <c r="D152" s="21" t="inlineStr">
         <is>
           <t>[15:0]</t>
         </is>
       </c>
-      <c r="E136" s="21" t="inlineStr">
+      <c r="E152" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F136" s="21" t="inlineStr">
+      <c r="F152" s="21" t="inlineStr">
         <is>
           <t>0xA0</t>
         </is>
       </c>
-      <c r="G136" s="21" t="inlineStr">
+      <c r="G152" s="21" t="inlineStr">
         <is>
           <t>RESET# low to CS# low time. Number of CK periods from the start of RESET# low to the first CS# low.
 Usage: program it while hr_ctrl.en = 0; it must cover the device tRPH (400 ns on the target devices).
@@ -4897,85 +5425,85 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="20.5" customHeight="1">
-      <c r="A137" s="22" t="inlineStr">
+    <row r="153" ht="20.5" customHeight="1">
+      <c r="A153" s="22" t="inlineStr">
         <is>
           <t>hr_d0_tvcs</t>
         </is>
       </c>
-      <c r="B137" s="22" t="inlineStr">
+      <c r="B153" s="22" t="inlineStr">
         <is>
           <t>0x10C</t>
         </is>
       </c>
-      <c r="C137" s="22" t="n"/>
-      <c r="D137" s="22" t="n"/>
-      <c r="E137" s="22" t="n"/>
-      <c r="F137" s="22" t="inlineStr">
+      <c r="C153" s="22" t="n"/>
+      <c r="D153" s="22" t="n"/>
+      <c r="E153" s="22" t="n"/>
+      <c r="F153" s="22" t="inlineStr">
         <is>
           <t>0x00009C40</t>
         </is>
       </c>
-      <c r="G137" s="22" t="inlineStr">
+      <c r="G153" s="22" t="inlineStr">
         <is>
           <t>Chip select 0 power-up time register. Sets the wait before the first access after power-up.</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="38" customHeight="1">
-      <c r="A138" s="21" t="n"/>
-      <c r="B138" s="21" t="n"/>
-      <c r="C138" s="21" t="inlineStr">
+    <row r="154" ht="38" customHeight="1">
+      <c r="A154" s="21" t="n"/>
+      <c r="B154" s="21" t="n"/>
+      <c r="C154" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D138" s="21" t="inlineStr">
+      <c r="D154" s="21" t="inlineStr">
         <is>
           <t>[31:16]</t>
         </is>
       </c>
-      <c r="E138" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F138" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G138" s="21" t="inlineStr">
+      <c r="E154" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F154" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G154" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="195.5" customHeight="1">
-      <c r="A139" s="21" t="n"/>
-      <c r="B139" s="21" t="n"/>
-      <c r="C139" s="21" t="inlineStr">
+    <row r="155" ht="195.5" customHeight="1">
+      <c r="A155" s="21" t="n"/>
+      <c r="B155" s="21" t="n"/>
+      <c r="C155" s="21" t="inlineStr">
         <is>
           <t>t_vcs</t>
         </is>
       </c>
-      <c r="D139" s="21" t="inlineStr">
+      <c r="D155" s="21" t="inlineStr">
         <is>
           <t>[15:0]</t>
         </is>
       </c>
-      <c r="E139" s="21" t="inlineStr">
+      <c r="E155" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F139" s="21" t="inlineStr">
+      <c r="F155" s="21" t="inlineStr">
         <is>
           <t>0x9C40</t>
         </is>
       </c>
-      <c r="G139" s="21" t="inlineStr">
+      <c r="G155" s="21" t="inlineStr">
         <is>
           <t>Power-up wait. Number of CK periods from VCC valid and RESET# high to the first access (device tVCS).
 Usage: program it while hr_ctrl.en = 0; it must cover the device tVCS (150 us on the target devices).
@@ -4987,85 +5515,85 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="20.5" customHeight="1">
-      <c r="A140" s="22" t="inlineStr">
+    <row r="156" ht="20.5" customHeight="1">
+      <c r="A156" s="22" t="inlineStr">
         <is>
           <t>hr_d0_tmin</t>
         </is>
       </c>
-      <c r="B140" s="22" t="inlineStr">
+      <c r="B156" s="22" t="inlineStr">
         <is>
           <t>0x110</t>
         </is>
       </c>
-      <c r="C140" s="22" t="n"/>
-      <c r="D140" s="22" t="n"/>
-      <c r="E140" s="22" t="n"/>
-      <c r="F140" s="22" t="inlineStr">
+      <c r="C156" s="22" t="n"/>
+      <c r="D156" s="22" t="n"/>
+      <c r="E156" s="22" t="n"/>
+      <c r="F156" s="22" t="inlineStr">
         <is>
           <t>0x00020702</t>
         </is>
       </c>
-      <c r="G140" s="22" t="inlineStr">
+      <c r="G156" s="22" t="inlineStr">
         <is>
           <t>Chip select 0 minimum wait register. Sets the minimum CS# high time, read-write recovery and CS# setup.</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="38" customHeight="1">
-      <c r="A141" s="21" t="n"/>
-      <c r="B141" s="21" t="n"/>
-      <c r="C141" s="21" t="inlineStr">
+    <row r="157" ht="38" customHeight="1">
+      <c r="A157" s="21" t="n"/>
+      <c r="B157" s="21" t="n"/>
+      <c r="C157" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D141" s="21" t="inlineStr">
+      <c r="D157" s="21" t="inlineStr">
         <is>
           <t>[31:24]</t>
         </is>
       </c>
-      <c r="E141" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F141" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G141" s="21" t="inlineStr">
+      <c r="E157" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F157" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G157" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="195.5" customHeight="1">
-      <c r="A142" s="21" t="n"/>
-      <c r="B142" s="21" t="n"/>
-      <c r="C142" s="21" t="inlineStr">
+    <row r="158" ht="195.5" customHeight="1">
+      <c r="A158" s="21" t="n"/>
+      <c r="B158" s="21" t="n"/>
+      <c r="C158" s="21" t="inlineStr">
         <is>
           <t>t_css</t>
         </is>
       </c>
-      <c r="D142" s="21" t="inlineStr">
+      <c r="D158" s="21" t="inlineStr">
         <is>
           <t>[23:16]</t>
         </is>
       </c>
-      <c r="E142" s="21" t="inlineStr">
+      <c r="E158" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F142" s="21" t="inlineStr">
+      <c r="F158" s="21" t="inlineStr">
         <is>
           <t>0x2</t>
         </is>
       </c>
-      <c r="G142" s="21" t="inlineStr">
+      <c r="G158" s="21" t="inlineStr">
         <is>
           <t>CS# setup time. Number of CK periods between CS# going low and the first CK edge (device tCSS).
 Usage: program it while hr_ctrl.en = 0; the target devices need 3 to 4 ns.
@@ -5077,30 +5605,30 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="213" customHeight="1">
-      <c r="A143" s="21" t="n"/>
-      <c r="B143" s="21" t="n"/>
-      <c r="C143" s="21" t="inlineStr">
+    <row r="159" ht="213" customHeight="1">
+      <c r="A159" s="21" t="n"/>
+      <c r="B159" s="21" t="n"/>
+      <c r="C159" s="21" t="inlineStr">
         <is>
           <t>t_rwr</t>
         </is>
       </c>
-      <c r="D143" s="21" t="inlineStr">
+      <c r="D159" s="21" t="inlineStr">
         <is>
           <t>[15:8]</t>
         </is>
       </c>
-      <c r="E143" s="21" t="inlineStr">
+      <c r="E159" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F143" s="21" t="inlineStr">
+      <c r="F159" s="21" t="inlineStr">
         <is>
           <t>0x7</t>
         </is>
       </c>
-      <c r="G143" s="21" t="inlineStr">
+      <c r="G159" s="21" t="inlineStr">
         <is>
           <t>Read-write recovery time. Minimum number of CK periods from the CS# rising edge of one transaction to the end of the CA1 phase of the next transaction to the same device (device tRWR).
 Usage: program it while hr_ctrl.en = 0; it sets the real gap between two transactions together with t_cshi.
@@ -5112,30 +5640,30 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="195.5" customHeight="1">
-      <c r="A144" s="21" t="n"/>
-      <c r="B144" s="21" t="n"/>
-      <c r="C144" s="21" t="inlineStr">
+    <row r="160" ht="195.5" customHeight="1">
+      <c r="A160" s="21" t="n"/>
+      <c r="B160" s="21" t="n"/>
+      <c r="C160" s="21" t="inlineStr">
         <is>
           <t>t_cshi</t>
         </is>
       </c>
-      <c r="D144" s="21" t="inlineStr">
+      <c r="D160" s="21" t="inlineStr">
         <is>
           <t>[7:0]</t>
         </is>
       </c>
-      <c r="E144" s="21" t="inlineStr">
+      <c r="E160" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F144" s="21" t="inlineStr">
+      <c r="F160" s="21" t="inlineStr">
         <is>
           <t>0x2</t>
         </is>
       </c>
-      <c r="G144" s="21" t="inlineStr">
+      <c r="G160" s="21" t="inlineStr">
         <is>
           <t>CS# high time. Minimum number of CK periods that CS# stays high between two transactions to this device (device tCSHI).
 Usage: program it while hr_ctrl.en = 0; the target devices need 6 ns or less.
@@ -5147,85 +5675,85 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="20.5" customHeight="1">
-      <c r="A145" s="22" t="inlineStr">
+    <row r="161" ht="20.5" customHeight="1">
+      <c r="A161" s="22" t="inlineStr">
         <is>
           <t>hr_d0_tcsm</t>
         </is>
       </c>
-      <c r="B145" s="22" t="inlineStr">
+      <c r="B161" s="22" t="inlineStr">
         <is>
           <t>0x114</t>
         </is>
       </c>
-      <c r="C145" s="22" t="n"/>
-      <c r="D145" s="22" t="n"/>
-      <c r="E145" s="22" t="n"/>
-      <c r="F145" s="22" t="inlineStr">
+      <c r="C161" s="22" t="n"/>
+      <c r="D161" s="22" t="n"/>
+      <c r="E161" s="22" t="n"/>
+      <c r="F161" s="22" t="inlineStr">
         <is>
           <t>0x000000A0</t>
         </is>
       </c>
-      <c r="G145" s="22" t="inlineStr">
+      <c r="G161" s="22" t="inlineStr">
         <is>
           <t>Chip select 0 CS# low limit register. Sets the longest time CS# may stay low.</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="38" customHeight="1">
-      <c r="A146" s="21" t="n"/>
-      <c r="B146" s="21" t="n"/>
-      <c r="C146" s="21" t="inlineStr">
+    <row r="162" ht="38" customHeight="1">
+      <c r="A162" s="21" t="n"/>
+      <c r="B162" s="21" t="n"/>
+      <c r="C162" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D146" s="21" t="inlineStr">
+      <c r="D162" s="21" t="inlineStr">
         <is>
           <t>[31:16]</t>
         </is>
       </c>
-      <c r="E146" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F146" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G146" s="21" t="inlineStr">
+      <c r="E162" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F162" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G162" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="230.5" customHeight="1">
-      <c r="A147" s="21" t="n"/>
-      <c r="B147" s="21" t="n"/>
-      <c r="C147" s="21" t="inlineStr">
+    <row r="163" ht="230.5" customHeight="1">
+      <c r="A163" s="21" t="n"/>
+      <c r="B163" s="21" t="n"/>
+      <c r="C163" s="21" t="inlineStr">
         <is>
           <t>t_csm</t>
         </is>
       </c>
-      <c r="D147" s="21" t="inlineStr">
+      <c r="D163" s="21" t="inlineStr">
         <is>
           <t>[15:0]</t>
         </is>
       </c>
-      <c r="E147" s="21" t="inlineStr">
+      <c r="E163" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F147" s="21" t="inlineStr">
+      <c r="F163" s="21" t="inlineStr">
         <is>
           <t>0xA0</t>
         </is>
       </c>
-      <c r="G147" s="21" t="inlineStr">
+      <c r="G163" s="21" t="inlineStr">
         <is>
           <t>CS# low limit. Maximum number of CK periods from CS# low to CS# high, including the command, latency and data phases; the controller splits longer transfers (device tCSM).
 Usage: set it for the device and its operating temperature (1 us above 85 C on some devices, 4 us otherwise); a larger value gives fewer transaction restarts and higher throughput.
@@ -5237,85 +5765,85 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="20.5" customHeight="1">
-      <c r="A148" s="22" t="inlineStr">
+    <row r="164" ht="20.5" customHeight="1">
+      <c r="A164" s="22" t="inlineStr">
         <is>
           <t>hr_d0_rcap</t>
         </is>
       </c>
-      <c r="B148" s="22" t="inlineStr">
+      <c r="B164" s="22" t="inlineStr">
         <is>
           <t>0x118</t>
         </is>
       </c>
-      <c r="C148" s="22" t="n"/>
-      <c r="D148" s="22" t="n"/>
-      <c r="E148" s="22" t="n"/>
-      <c r="F148" s="22" t="inlineStr">
+      <c r="C164" s="22" t="n"/>
+      <c r="D164" s="22" t="n"/>
+      <c r="E164" s="22" t="n"/>
+      <c r="F164" s="22" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
-      <c r="G148" s="22" t="inlineStr">
+      <c r="G164" s="22" t="inlineStr">
         <is>
           <t>Chip select 0 read capture register. Sets the delay-line tap used to capture read data.</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="38" customHeight="1">
-      <c r="A149" s="21" t="n"/>
-      <c r="B149" s="21" t="n"/>
-      <c r="C149" s="21" t="inlineStr">
+    <row r="165" ht="38" customHeight="1">
+      <c r="A165" s="21" t="n"/>
+      <c r="B165" s="21" t="n"/>
+      <c r="C165" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D149" s="21" t="inlineStr">
+      <c r="D165" s="21" t="inlineStr">
         <is>
           <t>[31:8]</t>
         </is>
       </c>
-      <c r="E149" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F149" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G149" s="21" t="inlineStr">
+      <c r="E165" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F165" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G165" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="213" customHeight="1">
-      <c r="A150" s="21" t="n"/>
-      <c r="B150" s="21" t="n"/>
-      <c r="C150" s="21" t="inlineStr">
+    <row r="166" ht="213" customHeight="1">
+      <c r="A166" s="21" t="n"/>
+      <c r="B166" s="21" t="n"/>
+      <c r="C166" s="21" t="inlineStr">
         <is>
           <t>tap</t>
         </is>
       </c>
-      <c r="D150" s="21" t="inlineStr">
+      <c r="D166" s="21" t="inlineStr">
         <is>
           <t>[7:0]</t>
         </is>
       </c>
-      <c r="E150" s="21" t="inlineStr">
+      <c r="E166" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F150" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G150" s="21" t="inlineStr">
+      <c r="F166" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G166" s="21" t="inlineStr">
         <is>
           <t>Delay-line tap. Code sent to the external delay line that delays RWDS so that its edges fall in the middle of the read data of this device.
 Usage: program it while hr_ctrl.en = 0 and tune it on the board; it is applied between transactions. Only the low hr_cap.dly_w bits are used.
@@ -5326,85 +5854,85 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="20.5" customHeight="1">
-      <c r="A151" s="22" t="inlineStr">
+    <row r="167" ht="20.5" customHeight="1">
+      <c r="A167" s="22" t="inlineStr">
         <is>
           <t>hr_d0_id</t>
         </is>
       </c>
-      <c r="B151" s="22" t="inlineStr">
+      <c r="B167" s="22" t="inlineStr">
         <is>
           <t>0x11C</t>
         </is>
       </c>
-      <c r="C151" s="22" t="n"/>
-      <c r="D151" s="22" t="n"/>
-      <c r="E151" s="22" t="n"/>
-      <c r="F151" s="22" t="inlineStr">
+      <c r="C167" s="22" t="n"/>
+      <c r="D167" s="22" t="n"/>
+      <c r="E167" s="22" t="n"/>
+      <c r="F167" s="22" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
-      <c r="G151" s="22" t="inlineStr">
+      <c r="G167" s="22" t="inlineStr">
         <is>
           <t>Chip select 0 device ID check register. Holds the expected device ID and enables the check.</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="38" customHeight="1">
-      <c r="A152" s="21" t="n"/>
-      <c r="B152" s="21" t="n"/>
-      <c r="C152" s="21" t="inlineStr">
+    <row r="168" ht="38" customHeight="1">
+      <c r="A168" s="21" t="n"/>
+      <c r="B168" s="21" t="n"/>
+      <c r="C168" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D152" s="21" t="inlineStr">
+      <c r="D168" s="21" t="inlineStr">
         <is>
           <t>[31:17]</t>
         </is>
       </c>
-      <c r="E152" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F152" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G152" s="21" t="inlineStr">
+      <c r="E168" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F168" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G168" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="195.5" customHeight="1">
-      <c r="A153" s="21" t="n"/>
-      <c r="B153" s="21" t="n"/>
-      <c r="C153" s="21" t="inlineStr">
+    <row r="169" ht="195.5" customHeight="1">
+      <c r="A169" s="21" t="n"/>
+      <c r="B169" s="21" t="n"/>
+      <c r="C169" s="21" t="inlineStr">
         <is>
           <t>id_chk_en</t>
         </is>
       </c>
-      <c r="D153" s="21" t="inlineStr">
+      <c r="D169" s="21" t="inlineStr">
         <is>
           <t>[16]</t>
         </is>
       </c>
-      <c r="E153" s="21" t="inlineStr">
+      <c r="E169" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F153" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G153" s="21" t="inlineStr">
+      <c r="F169" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G169" s="21" t="inlineStr">
         <is>
           <t>ID check enable. Enables the comparison of the device ID0 with id0_exp after start-up.
 Usage: program it while hr_ctrl.en = 0; a mismatch sets hr_irq_raw.id_mis and does not block AXI access.
@@ -5416,33 +5944,33 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="195.5" customHeight="1">
-      <c r="A154" s="21" t="n"/>
-      <c r="B154" s="21" t="n"/>
-      <c r="C154" s="21" t="inlineStr">
+    <row r="170" ht="195.5" customHeight="1">
+      <c r="A170" s="21" t="n"/>
+      <c r="B170" s="21" t="n"/>
+      <c r="C170" s="21" t="inlineStr">
         <is>
           <t>id0_exp</t>
         </is>
       </c>
-      <c r="D154" s="21" t="inlineStr">
+      <c r="D170" s="21" t="inlineStr">
         <is>
           <t>[15:0]</t>
         </is>
       </c>
-      <c r="E154" s="21" t="inlineStr">
+      <c r="E170" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F154" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G154" s="21" t="inlineStr">
+      <c r="F170" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G170" s="21" t="inlineStr">
         <is>
           <t>Expected ID0 value. The value that the controller compares with the ID0 register of the device after start-up.
-Usage: program it while hr_ctrl.en = 0, or load it with a preset; it is used only when id_chk_en = 1.
+Usage: program it while hr_ctrl.en = 0; it is used only when id_chk_en = 1.
 Values:
 0x0000 no expected value (reset value);
 0x0001 to 0xFFFF ID0 of the device.
@@ -5451,85 +5979,265 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="20.5" customHeight="1">
-      <c r="A155" s="22" t="inlineStr">
-        <is>
-          <t>hr_d1_cfg</t>
-        </is>
-      </c>
-      <c r="B155" s="22" t="inlineStr">
-        <is>
-          <t>0x200</t>
-        </is>
-      </c>
-      <c r="C155" s="22" t="n"/>
-      <c r="D155" s="22" t="n"/>
-      <c r="E155" s="22" t="n"/>
-      <c r="F155" s="22" t="inlineStr">
-        <is>
-          <t>0x0001C4E0</t>
-        </is>
-      </c>
-      <c r="G155" s="22" t="inlineStr">
-        <is>
-          <t>Chip select 1 device configuration register. Selects the device preset and the latency and mode values written to the device.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="38" customHeight="1">
-      <c r="A156" s="21" t="n"/>
-      <c r="B156" s="21" t="n"/>
-      <c r="C156" s="21" t="inlineStr">
+    <row r="171" ht="20.5" customHeight="1">
+      <c r="A171" s="22" t="inlineStr">
+        <is>
+          <t>hr_d0_tmo</t>
+        </is>
+      </c>
+      <c r="B171" s="22" t="inlineStr">
+        <is>
+          <t>0x120</t>
+        </is>
+      </c>
+      <c r="C171" s="22" t="n"/>
+      <c r="D171" s="22" t="n"/>
+      <c r="E171" s="22" t="n"/>
+      <c r="F171" s="22" t="inlineStr">
+        <is>
+          <t>0x00000200</t>
+        </is>
+      </c>
+      <c r="G171" s="22" t="inlineStr">
+        <is>
+          <t>Chip select 0 timeout register. Sets the longest time the controller waits for the device in one step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="38" customHeight="1">
+      <c r="A172" s="21" t="n"/>
+      <c r="B172" s="21" t="n"/>
+      <c r="C172" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D156" s="21" t="inlineStr">
-        <is>
-          <t>[31:20]</t>
-        </is>
-      </c>
-      <c r="E156" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F156" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G156" s="21" t="inlineStr">
+      <c r="D172" s="21" t="inlineStr">
+        <is>
+          <t>[31:16]</t>
+        </is>
+      </c>
+      <c r="E172" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F172" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G172" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="195.5" customHeight="1">
-      <c r="A157" s="21" t="n"/>
-      <c r="B157" s="21" t="n"/>
-      <c r="C157" s="21" t="inlineStr">
+    <row r="173" ht="248" customHeight="1">
+      <c r="A173" s="21" t="n"/>
+      <c r="B173" s="21" t="n"/>
+      <c r="C173" s="21" t="inlineStr">
+        <is>
+          <t>t_tmo</t>
+        </is>
+      </c>
+      <c r="D173" s="21" t="inlineStr">
+        <is>
+          <t>[15:0]</t>
+        </is>
+      </c>
+      <c r="E173" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F173" s="21" t="inlineStr">
+        <is>
+          <t>0x200</t>
+        </is>
+      </c>
+      <c r="G173" s="21" t="inlineStr">
+        <is>
+          <t>Device wait time. Maximum number of CK periods the controller waits for one answer of the device (read data strobe after the initial latency, next strobe edge in a burst) before it declares a timeout.
+Usage: program it while hr_ctrl.en = 0; the action after a timeout is chosen by hr_ctrl.tmo_act. The value must be longer than the longest legal wait of the device (initial latency 2 x init_lat plus refresh) so that no healthy access times out.
+Values:
+0x0000 timeout disabled;
+0x0001 to 0x000F illegal;
+0x0010 to 0xFFFF number of CK periods (reset value 0x0200, that is 2.56 us at 200 MHz).
+Unit: CK periods.
+Limits: values 1 to 15 are illegal (cfg_valid = 0); rescale it when hr_clk.ck_div changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="20.5" customHeight="1">
+      <c r="A174" s="22" t="inlineStr">
+        <is>
+          <t>hr_d0_idr</t>
+        </is>
+      </c>
+      <c r="B174" s="22" t="inlineStr">
+        <is>
+          <t>0x124</t>
+        </is>
+      </c>
+      <c r="C174" s="22" t="n"/>
+      <c r="D174" s="22" t="n"/>
+      <c r="E174" s="22" t="n"/>
+      <c r="F174" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G174" s="22" t="inlineStr">
+        <is>
+          <t>Chip select 0 device ID0 register. Holds the ID0 value that the controller read from the device at start-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="38" customHeight="1">
+      <c r="A175" s="21" t="n"/>
+      <c r="B175" s="21" t="n"/>
+      <c r="C175" s="21" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D175" s="21" t="inlineStr">
+        <is>
+          <t>[31:16]</t>
+        </is>
+      </c>
+      <c r="E175" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F175" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G175" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="213" customHeight="1">
+      <c r="A176" s="21" t="n"/>
+      <c r="B176" s="21" t="n"/>
+      <c r="C176" s="21" t="inlineStr">
+        <is>
+          <t>id0_act</t>
+        </is>
+      </c>
+      <c r="D176" s="21" t="inlineStr">
+        <is>
+          <t>[15:0]</t>
+        </is>
+      </c>
+      <c r="E176" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F176" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G176" s="21" t="inlineStr">
+        <is>
+          <t>Actual ID0. The 16-bit ID0 register of the device (row address bits, column address bits and manufacturer) read by the controller after start-up.
+Usage: read-only; valid after hr_sts.init_done = 1; compare it with the datasheet of the device, or read ID0 again at any time through the device command port (hr_cmd with the ID0 register address in hr_cmd_addr).
+Values:
+0x0000 to 0xFFFF ID0 value read from the device.
+Unit: none.
+Limits: 0x0000 before the start-up read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="20.5" customHeight="1">
+      <c r="A177" s="22" t="inlineStr">
+        <is>
+          <t>hr_d1_cfg</t>
+        </is>
+      </c>
+      <c r="B177" s="22" t="inlineStr">
+        <is>
+          <t>0x200</t>
+        </is>
+      </c>
+      <c r="C177" s="22" t="n"/>
+      <c r="D177" s="22" t="n"/>
+      <c r="E177" s="22" t="n"/>
+      <c r="F177" s="22" t="inlineStr">
+        <is>
+          <t>0x0001C4E0</t>
+        </is>
+      </c>
+      <c r="G177" s="22" t="inlineStr">
+        <is>
+          <t>Chip select 1 device configuration register. Holds the latency and mode values written to the device.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="38" customHeight="1">
+      <c r="A178" s="21" t="n"/>
+      <c r="B178" s="21" t="n"/>
+      <c r="C178" s="21" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D178" s="21" t="inlineStr">
+        <is>
+          <t>[31:20]</t>
+        </is>
+      </c>
+      <c r="E178" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F178" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G178" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="195.5" customHeight="1">
+      <c r="A179" s="21" t="n"/>
+      <c r="B179" s="21" t="n"/>
+      <c r="C179" s="21" t="inlineStr">
         <is>
           <t>pasr</t>
         </is>
       </c>
-      <c r="D157" s="21" t="inlineStr">
+      <c r="D179" s="21" t="inlineStr">
         <is>
           <t>[19:17]</t>
         </is>
       </c>
-      <c r="E157" s="21" t="inlineStr">
+      <c r="E179" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F157" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G157" s="21" t="inlineStr">
+      <c r="F179" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G179" s="21" t="inlineStr">
         <is>
           <t>Partial array refresh code. Value written into CR1[4:2] to choose which part of the array is refreshed.
 Usage: program it while hr_ctrl.en = 0; the data outside the refreshed part is lost.
@@ -5541,30 +6249,30 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="248" customHeight="1">
-      <c r="A158" s="21" t="n"/>
-      <c r="B158" s="21" t="n"/>
-      <c r="C158" s="21" t="inlineStr">
+    <row r="180" ht="248" customHeight="1">
+      <c r="A180" s="21" t="n"/>
+      <c r="B180" s="21" t="n"/>
+      <c r="C180" s="21" t="inlineStr">
         <is>
           <t>blen</t>
         </is>
       </c>
-      <c r="D158" s="21" t="inlineStr">
+      <c r="D180" s="21" t="inlineStr">
         <is>
           <t>[16:15]</t>
         </is>
       </c>
-      <c r="E158" s="21" t="inlineStr">
+      <c r="E180" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F158" s="21" t="inlineStr">
+      <c r="F180" s="21" t="inlineStr">
         <is>
           <t>0x3</t>
         </is>
       </c>
-      <c r="G158" s="21" t="inlineStr">
+      <c r="G180" s="21" t="inlineStr">
         <is>
           <t>Wrapped burst group size. Value written into CR0[1:0]; an AXI WRAP burst of the same byte length is sent as one wrapped HyperBus burst, others are split into two linear bursts.
 Usage: program it while hr_ctrl.en = 0; choose the cache line size of the system for critical-word-first reads.
@@ -5578,30 +6286,30 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="195.5" customHeight="1">
-      <c r="A159" s="21" t="n"/>
-      <c r="B159" s="21" t="n"/>
-      <c r="C159" s="21" t="inlineStr">
+    <row r="181" ht="195.5" customHeight="1">
+      <c r="A181" s="21" t="n"/>
+      <c r="B181" s="21" t="n"/>
+      <c r="C181" s="21" t="inlineStr">
         <is>
           <t>hybrid</t>
         </is>
       </c>
-      <c r="D159" s="21" t="inlineStr">
+      <c r="D181" s="21" t="inlineStr">
         <is>
           <t>[14]</t>
         </is>
       </c>
-      <c r="E159" s="21" t="inlineStr">
+      <c r="E181" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F159" s="21" t="inlineStr">
+      <c r="F181" s="21" t="inlineStr">
         <is>
           <t>0x1</t>
         </is>
       </c>
-      <c r="G159" s="21" t="inlineStr">
+      <c r="G181" s="21" t="inlineStr">
         <is>
           <t>Hybrid burst control. Value written into CR0[2], which selects how a wrapped burst continues after the wrap group.
 Usage: program it while hr_ctrl.en = 0; it matters only for wrapped bursts of the devices that support hybrid burst.
@@ -5613,30 +6321,30 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="178" customHeight="1">
-      <c r="A160" s="21" t="n"/>
-      <c r="B160" s="21" t="n"/>
-      <c r="C160" s="21" t="inlineStr">
+    <row r="182" ht="178" customHeight="1">
+      <c r="A182" s="21" t="n"/>
+      <c r="B182" s="21" t="n"/>
+      <c r="C182" s="21" t="inlineStr">
         <is>
           <t>drive</t>
         </is>
       </c>
-      <c r="D160" s="21" t="inlineStr">
+      <c r="D182" s="21" t="inlineStr">
         <is>
           <t>[13:11]</t>
         </is>
       </c>
-      <c r="E160" s="21" t="inlineStr">
+      <c r="E182" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F160" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G160" s="21" t="inlineStr">
+      <c r="F182" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G182" s="21" t="inlineStr">
         <is>
           <t>Output drive strength code. Value written into CR0[14:12] to set the output impedance of the DQ and RWDS drivers of the device.
 Usage: program it while hr_ctrl.en = 0; choose it for the board; the code meaning is given in the device datasheet.
@@ -5647,30 +6355,30 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="230.5" customHeight="1">
-      <c r="A161" s="21" t="n"/>
-      <c r="B161" s="21" t="n"/>
-      <c r="C161" s="21" t="inlineStr">
+    <row r="183" ht="230.5" customHeight="1">
+      <c r="A183" s="21" t="n"/>
+      <c r="B183" s="21" t="n"/>
+      <c r="C183" s="21" t="inlineStr">
         <is>
           <t>fixed_lat</t>
         </is>
       </c>
-      <c r="D161" s="21" t="inlineStr">
+      <c r="D183" s="21" t="inlineStr">
         <is>
           <t>[10]</t>
         </is>
       </c>
-      <c r="E161" s="21" t="inlineStr">
+      <c r="E183" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F161" s="21" t="inlineStr">
+      <c r="F183" s="21" t="inlineStr">
         <is>
           <t>0x1</t>
         </is>
       </c>
-      <c r="G161" s="21" t="inlineStr">
+      <c r="G183" s="21" t="inlineStr">
         <is>
           <t>Fixed latency enable. Selects whether the latency is always twice the initial latency or follows RWDS in the command and address phase; written into CR0[3].
 Usage: program it while hr_ctrl.en = 0 together with init_lat. In variable mode the controller samples RWDS during the CA phase and waits 1x or 2x init_lat.
@@ -5682,30 +6390,30 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="230.5" customHeight="1">
-      <c r="A162" s="21" t="n"/>
-      <c r="B162" s="21" t="n"/>
-      <c r="C162" s="21" t="inlineStr">
+    <row r="184" ht="230.5" customHeight="1">
+      <c r="A184" s="21" t="n"/>
+      <c r="B184" s="21" t="n"/>
+      <c r="C184" s="21" t="inlineStr">
         <is>
           <t>init_lat</t>
         </is>
       </c>
-      <c r="D162" s="21" t="inlineStr">
+      <c r="D184" s="21" t="inlineStr">
         <is>
           <t>[9:5]</t>
         </is>
       </c>
-      <c r="E162" s="21" t="inlineStr">
+      <c r="E184" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F162" s="21" t="inlineStr">
+      <c r="F184" s="21" t="inlineStr">
         <is>
           <t>0x7</t>
         </is>
       </c>
-      <c r="G162" s="21" t="inlineStr">
+      <c r="G184" s="21" t="inlineStr">
         <is>
           <t>Initial latency. Number of CK periods the controller waits between the command and address phase and the first data; the controller encodes it into CR0[7:4] at start-up.
 Usage: program it while hr_ctrl.en = 0; with fixed latency the wait is twice this value. Keep it equal to the latency code in the device CR0, otherwise hr_irq_raw.lat_mis is set when CR0 is changed by software.
@@ -5717,130 +6425,85 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="230.5" customHeight="1">
-      <c r="A163" s="21" t="n"/>
-      <c r="B163" s="21" t="n"/>
-      <c r="C163" s="21" t="inlineStr">
-        <is>
-          <t>preset_go</t>
-        </is>
-      </c>
-      <c r="D163" s="21" t="inlineStr">
-        <is>
-          <t>[4]</t>
-        </is>
-      </c>
-      <c r="E163" s="21" t="inlineStr">
-        <is>
-          <t>rwi</t>
-        </is>
-      </c>
-      <c r="F163" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G163" s="21" t="inlineStr">
-        <is>
-          <t>Preset load command. Writing 1 copies the timing, latency and ID fields of the selected preset into the register group of chip select 1; hardware clears it when done.
-Usage: write 1 only while hr_ctrl.en = 0, after writing preset; a write while enabled is ignored and sets hr_irq_raw.cfg_err. A software write wins over the hardware clear in the same cycle.
-Values:
-0x0 no load (reset value);
-0x1 load the preset; reads 0x1 until the load is done.
-Unit: none.
-Limits: none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="318" customHeight="1">
-      <c r="A164" s="21" t="n"/>
-      <c r="B164" s="21" t="n"/>
-      <c r="C164" s="21" t="inlineStr">
-        <is>
-          <t>preset</t>
-        </is>
-      </c>
-      <c r="D164" s="21" t="inlineStr">
-        <is>
-          <t>[3:0]</t>
-        </is>
-      </c>
-      <c r="E164" s="21" t="inlineStr">
+    <row r="185" ht="38" customHeight="1">
+      <c r="A185" s="21" t="n"/>
+      <c r="B185" s="21" t="n"/>
+      <c r="C185" s="21" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D185" s="21" t="inlineStr">
+        <is>
+          <t>[4:0]</t>
+        </is>
+      </c>
+      <c r="E185" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F185" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G185" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20.5" customHeight="1">
+      <c r="A186" s="22" t="inlineStr">
+        <is>
+          <t>hr_d1_trst</t>
+        </is>
+      </c>
+      <c r="B186" s="22" t="inlineStr">
+        <is>
+          <t>0x204</t>
+        </is>
+      </c>
+      <c r="C186" s="22" t="n"/>
+      <c r="D186" s="22" t="n"/>
+      <c r="E186" s="22" t="n"/>
+      <c r="F186" s="22" t="inlineStr">
+        <is>
+          <t>0x00500050</t>
+        </is>
+      </c>
+      <c r="G186" s="22" t="inlineStr">
+        <is>
+          <t>Chip select 1 RESET# timing register. Sets the RESET# low time and the wait after RESET# is released.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="195.5" customHeight="1">
+      <c r="A187" s="21" t="n"/>
+      <c r="B187" s="21" t="n"/>
+      <c r="C187" s="21" t="inlineStr">
+        <is>
+          <t>t_rh</t>
+        </is>
+      </c>
+      <c r="D187" s="21" t="inlineStr">
+        <is>
+          <t>[31:16]</t>
+        </is>
+      </c>
+      <c r="E187" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F164" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G164" s="21" t="inlineStr">
-        <is>
-          <t>Device preset select. Chooses the set of default timing values of one target device that the load command copies into the register group of chip select 1.
-Usage: write it, then write preset_go = 1, while hr_ctrl.en = 0; you may overwrite any field afterwards. The loaded values are listed in the specification.
-Values:
-0x0 safe values for all target devices (reset value);
-0x1 S80KS2562;
-0x2 W958D8NBYA;
-0x3 IS66WVH32M8DALL;
-0x4 S80KS2564;
-0x5 W958D6NBKX;
-0x6 to 0xF reserved.
-Unit: none.
-Limits: do not write 0x6 to 0xF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="20.5" customHeight="1">
-      <c r="A165" s="22" t="inlineStr">
-        <is>
-          <t>hr_d1_trst</t>
-        </is>
-      </c>
-      <c r="B165" s="22" t="inlineStr">
-        <is>
-          <t>0x204</t>
-        </is>
-      </c>
-      <c r="C165" s="22" t="n"/>
-      <c r="D165" s="22" t="n"/>
-      <c r="E165" s="22" t="n"/>
-      <c r="F165" s="22" t="inlineStr">
-        <is>
-          <t>0x00500050</t>
-        </is>
-      </c>
-      <c r="G165" s="22" t="inlineStr">
-        <is>
-          <t>Chip select 1 RESET# timing register. Sets the RESET# low time and the wait after RESET# is released.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="195.5" customHeight="1">
-      <c r="A166" s="21" t="n"/>
-      <c r="B166" s="21" t="n"/>
-      <c r="C166" s="21" t="inlineStr">
-        <is>
-          <t>t_rh</t>
-        </is>
-      </c>
-      <c r="D166" s="21" t="inlineStr">
-        <is>
-          <t>[31:16]</t>
-        </is>
-      </c>
-      <c r="E166" s="21" t="inlineStr">
-        <is>
-          <t>rw</t>
-        </is>
-      </c>
-      <c r="F166" s="21" t="inlineStr">
+      <c r="F187" s="21" t="inlineStr">
         <is>
           <t>0x50</t>
         </is>
       </c>
-      <c r="G166" s="21" t="inlineStr">
+      <c r="G187" s="21" t="inlineStr">
         <is>
           <t>RESET# high to CS# low time. Number of CK periods the controller waits after RESET# is released before CS# may go low.
 Usage: program it while hr_ctrl.en = 0; it must cover the device tRH (200 ns on the target devices).
@@ -5852,30 +6515,30 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="213" customHeight="1">
-      <c r="A167" s="21" t="n"/>
-      <c r="B167" s="21" t="n"/>
-      <c r="C167" s="21" t="inlineStr">
+    <row r="188" ht="213" customHeight="1">
+      <c r="A188" s="21" t="n"/>
+      <c r="B188" s="21" t="n"/>
+      <c r="C188" s="21" t="inlineStr">
         <is>
           <t>t_rp</t>
         </is>
       </c>
-      <c r="D167" s="21" t="inlineStr">
+      <c r="D188" s="21" t="inlineStr">
         <is>
           <t>[15:0]</t>
         </is>
       </c>
-      <c r="E167" s="21" t="inlineStr">
+      <c r="E188" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F167" s="21" t="inlineStr">
+      <c r="F188" s="21" t="inlineStr">
         <is>
           <t>0x50</t>
         </is>
       </c>
-      <c r="G167" s="21" t="inlineStr">
+      <c r="G188" s="21" t="inlineStr">
         <is>
           <t>RESET# pulse width. Number of CK periods the controller holds RESET# low at start-up.
 Usage: program it while hr_ctrl.en = 0; with two chip selects the larger value of both groups is used; it must cover the device tRP (200 ns on the target devices).
@@ -5887,85 +6550,85 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="20.5" customHeight="1">
-      <c r="A168" s="22" t="inlineStr">
+    <row r="189" ht="20.5" customHeight="1">
+      <c r="A189" s="22" t="inlineStr">
         <is>
           <t>hr_d1_trph</t>
         </is>
       </c>
-      <c r="B168" s="22" t="inlineStr">
+      <c r="B189" s="22" t="inlineStr">
         <is>
           <t>0x208</t>
         </is>
       </c>
-      <c r="C168" s="22" t="n"/>
-      <c r="D168" s="22" t="n"/>
-      <c r="E168" s="22" t="n"/>
-      <c r="F168" s="22" t="inlineStr">
+      <c r="C189" s="22" t="n"/>
+      <c r="D189" s="22" t="n"/>
+      <c r="E189" s="22" t="n"/>
+      <c r="F189" s="22" t="inlineStr">
         <is>
           <t>0x000000A0</t>
         </is>
       </c>
-      <c r="G168" s="22" t="inlineStr">
+      <c r="G189" s="22" t="inlineStr">
         <is>
           <t>Chip select 1 RESET# low to CS# low register. Sets the wait from the start of RESET# to the first access.</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="38" customHeight="1">
-      <c r="A169" s="21" t="n"/>
-      <c r="B169" s="21" t="n"/>
-      <c r="C169" s="21" t="inlineStr">
+    <row r="190" ht="38" customHeight="1">
+      <c r="A190" s="21" t="n"/>
+      <c r="B190" s="21" t="n"/>
+      <c r="C190" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D169" s="21" t="inlineStr">
+      <c r="D190" s="21" t="inlineStr">
         <is>
           <t>[31:16]</t>
         </is>
       </c>
-      <c r="E169" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F169" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G169" s="21" t="inlineStr">
+      <c r="E190" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F190" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G190" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="195.5" customHeight="1">
-      <c r="A170" s="21" t="n"/>
-      <c r="B170" s="21" t="n"/>
-      <c r="C170" s="21" t="inlineStr">
+    <row r="191" ht="195.5" customHeight="1">
+      <c r="A191" s="21" t="n"/>
+      <c r="B191" s="21" t="n"/>
+      <c r="C191" s="21" t="inlineStr">
         <is>
           <t>t_rph</t>
         </is>
       </c>
-      <c r="D170" s="21" t="inlineStr">
+      <c r="D191" s="21" t="inlineStr">
         <is>
           <t>[15:0]</t>
         </is>
       </c>
-      <c r="E170" s="21" t="inlineStr">
+      <c r="E191" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F170" s="21" t="inlineStr">
+      <c r="F191" s="21" t="inlineStr">
         <is>
           <t>0xA0</t>
         </is>
       </c>
-      <c r="G170" s="21" t="inlineStr">
+      <c r="G191" s="21" t="inlineStr">
         <is>
           <t>RESET# low to CS# low time. Number of CK periods from the start of RESET# low to the first CS# low.
 Usage: program it while hr_ctrl.en = 0; it must cover the device tRPH (400 ns on the target devices).
@@ -5977,85 +6640,85 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="20.5" customHeight="1">
-      <c r="A171" s="22" t="inlineStr">
+    <row r="192" ht="20.5" customHeight="1">
+      <c r="A192" s="22" t="inlineStr">
         <is>
           <t>hr_d1_tvcs</t>
         </is>
       </c>
-      <c r="B171" s="22" t="inlineStr">
+      <c r="B192" s="22" t="inlineStr">
         <is>
           <t>0x20C</t>
         </is>
       </c>
-      <c r="C171" s="22" t="n"/>
-      <c r="D171" s="22" t="n"/>
-      <c r="E171" s="22" t="n"/>
-      <c r="F171" s="22" t="inlineStr">
+      <c r="C192" s="22" t="n"/>
+      <c r="D192" s="22" t="n"/>
+      <c r="E192" s="22" t="n"/>
+      <c r="F192" s="22" t="inlineStr">
         <is>
           <t>0x00009C40</t>
         </is>
       </c>
-      <c r="G171" s="22" t="inlineStr">
+      <c r="G192" s="22" t="inlineStr">
         <is>
           <t>Chip select 1 power-up time register. Sets the wait before the first access after power-up.</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="38" customHeight="1">
-      <c r="A172" s="21" t="n"/>
-      <c r="B172" s="21" t="n"/>
-      <c r="C172" s="21" t="inlineStr">
+    <row r="193" ht="38" customHeight="1">
+      <c r="A193" s="21" t="n"/>
+      <c r="B193" s="21" t="n"/>
+      <c r="C193" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D172" s="21" t="inlineStr">
+      <c r="D193" s="21" t="inlineStr">
         <is>
           <t>[31:16]</t>
         </is>
       </c>
-      <c r="E172" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F172" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G172" s="21" t="inlineStr">
+      <c r="E193" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F193" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G193" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="195.5" customHeight="1">
-      <c r="A173" s="21" t="n"/>
-      <c r="B173" s="21" t="n"/>
-      <c r="C173" s="21" t="inlineStr">
+    <row r="194" ht="195.5" customHeight="1">
+      <c r="A194" s="21" t="n"/>
+      <c r="B194" s="21" t="n"/>
+      <c r="C194" s="21" t="inlineStr">
         <is>
           <t>t_vcs</t>
         </is>
       </c>
-      <c r="D173" s="21" t="inlineStr">
+      <c r="D194" s="21" t="inlineStr">
         <is>
           <t>[15:0]</t>
         </is>
       </c>
-      <c r="E173" s="21" t="inlineStr">
+      <c r="E194" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F173" s="21" t="inlineStr">
+      <c r="F194" s="21" t="inlineStr">
         <is>
           <t>0x9C40</t>
         </is>
       </c>
-      <c r="G173" s="21" t="inlineStr">
+      <c r="G194" s="21" t="inlineStr">
         <is>
           <t>Power-up wait. Number of CK periods from VCC valid and RESET# high to the first access (device tVCS).
 Usage: program it while hr_ctrl.en = 0; it must cover the device tVCS (150 us on the target devices).
@@ -6067,85 +6730,85 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="20.5" customHeight="1">
-      <c r="A174" s="22" t="inlineStr">
+    <row r="195" ht="20.5" customHeight="1">
+      <c r="A195" s="22" t="inlineStr">
         <is>
           <t>hr_d1_tmin</t>
         </is>
       </c>
-      <c r="B174" s="22" t="inlineStr">
+      <c r="B195" s="22" t="inlineStr">
         <is>
           <t>0x210</t>
         </is>
       </c>
-      <c r="C174" s="22" t="n"/>
-      <c r="D174" s="22" t="n"/>
-      <c r="E174" s="22" t="n"/>
-      <c r="F174" s="22" t="inlineStr">
+      <c r="C195" s="22" t="n"/>
+      <c r="D195" s="22" t="n"/>
+      <c r="E195" s="22" t="n"/>
+      <c r="F195" s="22" t="inlineStr">
         <is>
           <t>0x00020702</t>
         </is>
       </c>
-      <c r="G174" s="22" t="inlineStr">
+      <c r="G195" s="22" t="inlineStr">
         <is>
           <t>Chip select 1 minimum wait register. Sets the minimum CS# high time, read-write recovery and CS# setup.</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="38" customHeight="1">
-      <c r="A175" s="21" t="n"/>
-      <c r="B175" s="21" t="n"/>
-      <c r="C175" s="21" t="inlineStr">
+    <row r="196" ht="38" customHeight="1">
+      <c r="A196" s="21" t="n"/>
+      <c r="B196" s="21" t="n"/>
+      <c r="C196" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D175" s="21" t="inlineStr">
+      <c r="D196" s="21" t="inlineStr">
         <is>
           <t>[31:24]</t>
         </is>
       </c>
-      <c r="E175" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F175" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G175" s="21" t="inlineStr">
+      <c r="E196" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F196" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G196" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="195.5" customHeight="1">
-      <c r="A176" s="21" t="n"/>
-      <c r="B176" s="21" t="n"/>
-      <c r="C176" s="21" t="inlineStr">
+    <row r="197" ht="195.5" customHeight="1">
+      <c r="A197" s="21" t="n"/>
+      <c r="B197" s="21" t="n"/>
+      <c r="C197" s="21" t="inlineStr">
         <is>
           <t>t_css</t>
         </is>
       </c>
-      <c r="D176" s="21" t="inlineStr">
+      <c r="D197" s="21" t="inlineStr">
         <is>
           <t>[23:16]</t>
         </is>
       </c>
-      <c r="E176" s="21" t="inlineStr">
+      <c r="E197" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F176" s="21" t="inlineStr">
+      <c r="F197" s="21" t="inlineStr">
         <is>
           <t>0x2</t>
         </is>
       </c>
-      <c r="G176" s="21" t="inlineStr">
+      <c r="G197" s="21" t="inlineStr">
         <is>
           <t>CS# setup time. Number of CK periods between CS# going low and the first CK edge (device tCSS).
 Usage: program it while hr_ctrl.en = 0; the target devices need 3 to 4 ns.
@@ -6157,30 +6820,30 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="213" customHeight="1">
-      <c r="A177" s="21" t="n"/>
-      <c r="B177" s="21" t="n"/>
-      <c r="C177" s="21" t="inlineStr">
+    <row r="198" ht="213" customHeight="1">
+      <c r="A198" s="21" t="n"/>
+      <c r="B198" s="21" t="n"/>
+      <c r="C198" s="21" t="inlineStr">
         <is>
           <t>t_rwr</t>
         </is>
       </c>
-      <c r="D177" s="21" t="inlineStr">
+      <c r="D198" s="21" t="inlineStr">
         <is>
           <t>[15:8]</t>
         </is>
       </c>
-      <c r="E177" s="21" t="inlineStr">
+      <c r="E198" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F177" s="21" t="inlineStr">
+      <c r="F198" s="21" t="inlineStr">
         <is>
           <t>0x7</t>
         </is>
       </c>
-      <c r="G177" s="21" t="inlineStr">
+      <c r="G198" s="21" t="inlineStr">
         <is>
           <t>Read-write recovery time. Minimum number of CK periods from the CS# rising edge of one transaction to the end of the CA1 phase of the next transaction to the same device (device tRWR).
 Usage: program it while hr_ctrl.en = 0; it sets the real gap between two transactions together with t_cshi.
@@ -6192,30 +6855,30 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="195.5" customHeight="1">
-      <c r="A178" s="21" t="n"/>
-      <c r="B178" s="21" t="n"/>
-      <c r="C178" s="21" t="inlineStr">
+    <row r="199" ht="195.5" customHeight="1">
+      <c r="A199" s="21" t="n"/>
+      <c r="B199" s="21" t="n"/>
+      <c r="C199" s="21" t="inlineStr">
         <is>
           <t>t_cshi</t>
         </is>
       </c>
-      <c r="D178" s="21" t="inlineStr">
+      <c r="D199" s="21" t="inlineStr">
         <is>
           <t>[7:0]</t>
         </is>
       </c>
-      <c r="E178" s="21" t="inlineStr">
+      <c r="E199" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F178" s="21" t="inlineStr">
+      <c r="F199" s="21" t="inlineStr">
         <is>
           <t>0x2</t>
         </is>
       </c>
-      <c r="G178" s="21" t="inlineStr">
+      <c r="G199" s="21" t="inlineStr">
         <is>
           <t>CS# high time. Minimum number of CK periods that CS# stays high between two transactions to this device (device tCSHI).
 Usage: program it while hr_ctrl.en = 0; the target devices need 6 ns or less.
@@ -6227,85 +6890,85 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="20.5" customHeight="1">
-      <c r="A179" s="22" t="inlineStr">
+    <row r="200" ht="20.5" customHeight="1">
+      <c r="A200" s="22" t="inlineStr">
         <is>
           <t>hr_d1_tcsm</t>
         </is>
       </c>
-      <c r="B179" s="22" t="inlineStr">
+      <c r="B200" s="22" t="inlineStr">
         <is>
           <t>0x214</t>
         </is>
       </c>
-      <c r="C179" s="22" t="n"/>
-      <c r="D179" s="22" t="n"/>
-      <c r="E179" s="22" t="n"/>
-      <c r="F179" s="22" t="inlineStr">
+      <c r="C200" s="22" t="n"/>
+      <c r="D200" s="22" t="n"/>
+      <c r="E200" s="22" t="n"/>
+      <c r="F200" s="22" t="inlineStr">
         <is>
           <t>0x000000A0</t>
         </is>
       </c>
-      <c r="G179" s="22" t="inlineStr">
+      <c r="G200" s="22" t="inlineStr">
         <is>
           <t>Chip select 1 CS# low limit register. Sets the longest time CS# may stay low.</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="38" customHeight="1">
-      <c r="A180" s="21" t="n"/>
-      <c r="B180" s="21" t="n"/>
-      <c r="C180" s="21" t="inlineStr">
+    <row r="201" ht="38" customHeight="1">
+      <c r="A201" s="21" t="n"/>
+      <c r="B201" s="21" t="n"/>
+      <c r="C201" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D180" s="21" t="inlineStr">
+      <c r="D201" s="21" t="inlineStr">
         <is>
           <t>[31:16]</t>
         </is>
       </c>
-      <c r="E180" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F180" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G180" s="21" t="inlineStr">
+      <c r="E201" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F201" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G201" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="230.5" customHeight="1">
-      <c r="A181" s="21" t="n"/>
-      <c r="B181" s="21" t="n"/>
-      <c r="C181" s="21" t="inlineStr">
+    <row r="202" ht="230.5" customHeight="1">
+      <c r="A202" s="21" t="n"/>
+      <c r="B202" s="21" t="n"/>
+      <c r="C202" s="21" t="inlineStr">
         <is>
           <t>t_csm</t>
         </is>
       </c>
-      <c r="D181" s="21" t="inlineStr">
+      <c r="D202" s="21" t="inlineStr">
         <is>
           <t>[15:0]</t>
         </is>
       </c>
-      <c r="E181" s="21" t="inlineStr">
+      <c r="E202" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F181" s="21" t="inlineStr">
+      <c r="F202" s="21" t="inlineStr">
         <is>
           <t>0xA0</t>
         </is>
       </c>
-      <c r="G181" s="21" t="inlineStr">
+      <c r="G202" s="21" t="inlineStr">
         <is>
           <t>CS# low limit. Maximum number of CK periods from CS# low to CS# high, including the command, latency and data phases; the controller splits longer transfers (device tCSM).
 Usage: set it for the device and its operating temperature (1 us above 85 C on some devices, 4 us otherwise); a larger value gives fewer transaction restarts and higher throughput.
@@ -6317,85 +6980,85 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="20.5" customHeight="1">
-      <c r="A182" s="22" t="inlineStr">
+    <row r="203" ht="20.5" customHeight="1">
+      <c r="A203" s="22" t="inlineStr">
         <is>
           <t>hr_d1_rcap</t>
         </is>
       </c>
-      <c r="B182" s="22" t="inlineStr">
+      <c r="B203" s="22" t="inlineStr">
         <is>
           <t>0x218</t>
         </is>
       </c>
-      <c r="C182" s="22" t="n"/>
-      <c r="D182" s="22" t="n"/>
-      <c r="E182" s="22" t="n"/>
-      <c r="F182" s="22" t="inlineStr">
+      <c r="C203" s="22" t="n"/>
+      <c r="D203" s="22" t="n"/>
+      <c r="E203" s="22" t="n"/>
+      <c r="F203" s="22" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
-      <c r="G182" s="22" t="inlineStr">
+      <c r="G203" s="22" t="inlineStr">
         <is>
           <t>Chip select 1 read capture register. Sets the delay-line tap used to capture read data.</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="38" customHeight="1">
-      <c r="A183" s="21" t="n"/>
-      <c r="B183" s="21" t="n"/>
-      <c r="C183" s="21" t="inlineStr">
+    <row r="204" ht="38" customHeight="1">
+      <c r="A204" s="21" t="n"/>
+      <c r="B204" s="21" t="n"/>
+      <c r="C204" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D183" s="21" t="inlineStr">
+      <c r="D204" s="21" t="inlineStr">
         <is>
           <t>[31:8]</t>
         </is>
       </c>
-      <c r="E183" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F183" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G183" s="21" t="inlineStr">
+      <c r="E204" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F204" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G204" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="213" customHeight="1">
-      <c r="A184" s="21" t="n"/>
-      <c r="B184" s="21" t="n"/>
-      <c r="C184" s="21" t="inlineStr">
+    <row r="205" ht="213" customHeight="1">
+      <c r="A205" s="21" t="n"/>
+      <c r="B205" s="21" t="n"/>
+      <c r="C205" s="21" t="inlineStr">
         <is>
           <t>tap</t>
         </is>
       </c>
-      <c r="D184" s="21" t="inlineStr">
+      <c r="D205" s="21" t="inlineStr">
         <is>
           <t>[7:0]</t>
         </is>
       </c>
-      <c r="E184" s="21" t="inlineStr">
+      <c r="E205" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F184" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G184" s="21" t="inlineStr">
+      <c r="F205" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G205" s="21" t="inlineStr">
         <is>
           <t>Delay-line tap. Code sent to the external delay line that delays RWDS so that its edges fall in the middle of the read data of this device.
 Usage: program it while hr_ctrl.en = 0 and tune it on the board; it is applied between transactions. Only the low hr_cap.dly_w bits are used.
@@ -6406,85 +7069,85 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="20.5" customHeight="1">
-      <c r="A185" s="22" t="inlineStr">
+    <row r="206" ht="20.5" customHeight="1">
+      <c r="A206" s="22" t="inlineStr">
         <is>
           <t>hr_d1_id</t>
         </is>
       </c>
-      <c r="B185" s="22" t="inlineStr">
+      <c r="B206" s="22" t="inlineStr">
         <is>
           <t>0x21C</t>
         </is>
       </c>
-      <c r="C185" s="22" t="n"/>
-      <c r="D185" s="22" t="n"/>
-      <c r="E185" s="22" t="n"/>
-      <c r="F185" s="22" t="inlineStr">
+      <c r="C206" s="22" t="n"/>
+      <c r="D206" s="22" t="n"/>
+      <c r="E206" s="22" t="n"/>
+      <c r="F206" s="22" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
-      <c r="G185" s="22" t="inlineStr">
+      <c r="G206" s="22" t="inlineStr">
         <is>
           <t>Chip select 1 device ID check register. Holds the expected device ID and enables the check.</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="38" customHeight="1">
-      <c r="A186" s="21" t="n"/>
-      <c r="B186" s="21" t="n"/>
-      <c r="C186" s="21" t="inlineStr">
+    <row r="207" ht="38" customHeight="1">
+      <c r="A207" s="21" t="n"/>
+      <c r="B207" s="21" t="n"/>
+      <c r="C207" s="21" t="inlineStr">
         <is>
           <t>reserved</t>
         </is>
       </c>
-      <c r="D186" s="21" t="inlineStr">
+      <c r="D207" s="21" t="inlineStr">
         <is>
           <t>[31:17]</t>
         </is>
       </c>
-      <c r="E186" s="21" t="inlineStr">
-        <is>
-          <t>ro</t>
-        </is>
-      </c>
-      <c r="F186" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G186" s="21" t="inlineStr">
+      <c r="E207" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F207" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G207" s="21" t="inlineStr">
         <is>
           <t>This field is unused.
 Read-as-zero and write-ignored.</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="195.5" customHeight="1">
-      <c r="A187" s="21" t="n"/>
-      <c r="B187" s="21" t="n"/>
-      <c r="C187" s="21" t="inlineStr">
+    <row r="208" ht="195.5" customHeight="1">
+      <c r="A208" s="21" t="n"/>
+      <c r="B208" s="21" t="n"/>
+      <c r="C208" s="21" t="inlineStr">
         <is>
           <t>id_chk_en</t>
         </is>
       </c>
-      <c r="D187" s="21" t="inlineStr">
+      <c r="D208" s="21" t="inlineStr">
         <is>
           <t>[16]</t>
         </is>
       </c>
-      <c r="E187" s="21" t="inlineStr">
+      <c r="E208" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F187" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G187" s="21" t="inlineStr">
+      <c r="F208" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G208" s="21" t="inlineStr">
         <is>
           <t>ID check enable. Enables the comparison of the device ID0 with id0_exp after start-up.
 Usage: program it while hr_ctrl.en = 0; a mismatch sets hr_irq_raw.id_mis and does not block AXI access.
@@ -6496,38 +7159,218 @@
         </is>
       </c>
     </row>
-    <row r="188" ht="195.5" customHeight="1">
-      <c r="A188" s="21" t="n"/>
-      <c r="B188" s="21" t="n"/>
-      <c r="C188" s="21" t="inlineStr">
+    <row r="209" ht="195.5" customHeight="1">
+      <c r="A209" s="21" t="n"/>
+      <c r="B209" s="21" t="n"/>
+      <c r="C209" s="21" t="inlineStr">
         <is>
           <t>id0_exp</t>
         </is>
       </c>
-      <c r="D188" s="21" t="inlineStr">
+      <c r="D209" s="21" t="inlineStr">
         <is>
           <t>[15:0]</t>
         </is>
       </c>
-      <c r="E188" s="21" t="inlineStr">
+      <c r="E209" s="21" t="inlineStr">
         <is>
           <t>rw</t>
         </is>
       </c>
-      <c r="F188" s="21" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="G188" s="21" t="inlineStr">
+      <c r="F209" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G209" s="21" t="inlineStr">
         <is>
           <t>Expected ID0 value. The value that the controller compares with the ID0 register of the device after start-up.
-Usage: program it while hr_ctrl.en = 0, or load it with a preset; it is used only when id_chk_en = 1.
+Usage: program it while hr_ctrl.en = 0; it is used only when id_chk_en = 1.
 Values:
 0x0000 no expected value (reset value);
 0x0001 to 0xFFFF ID0 of the device.
 Unit: none.
 Limits: none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="20.5" customHeight="1">
+      <c r="A210" s="22" t="inlineStr">
+        <is>
+          <t>hr_d1_tmo</t>
+        </is>
+      </c>
+      <c r="B210" s="22" t="inlineStr">
+        <is>
+          <t>0x220</t>
+        </is>
+      </c>
+      <c r="C210" s="22" t="n"/>
+      <c r="D210" s="22" t="n"/>
+      <c r="E210" s="22" t="n"/>
+      <c r="F210" s="22" t="inlineStr">
+        <is>
+          <t>0x00000200</t>
+        </is>
+      </c>
+      <c r="G210" s="22" t="inlineStr">
+        <is>
+          <t>Chip select 1 timeout register. Sets the longest time the controller waits for the device in one step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="38" customHeight="1">
+      <c r="A211" s="21" t="n"/>
+      <c r="B211" s="21" t="n"/>
+      <c r="C211" s="21" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D211" s="21" t="inlineStr">
+        <is>
+          <t>[31:16]</t>
+        </is>
+      </c>
+      <c r="E211" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F211" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G211" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="248" customHeight="1">
+      <c r="A212" s="21" t="n"/>
+      <c r="B212" s="21" t="n"/>
+      <c r="C212" s="21" t="inlineStr">
+        <is>
+          <t>t_tmo</t>
+        </is>
+      </c>
+      <c r="D212" s="21" t="inlineStr">
+        <is>
+          <t>[15:0]</t>
+        </is>
+      </c>
+      <c r="E212" s="21" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F212" s="21" t="inlineStr">
+        <is>
+          <t>0x200</t>
+        </is>
+      </c>
+      <c r="G212" s="21" t="inlineStr">
+        <is>
+          <t>Device wait time. Maximum number of CK periods the controller waits for one answer of the device (read data strobe after the initial latency, next strobe edge in a burst) before it declares a timeout.
+Usage: program it while hr_ctrl.en = 0; the action after a timeout is chosen by hr_ctrl.tmo_act. The value must be longer than the longest legal wait of the device (initial latency 2 x init_lat plus refresh) so that no healthy access times out.
+Values:
+0x0000 timeout disabled;
+0x0001 to 0x000F illegal;
+0x0010 to 0xFFFF number of CK periods (reset value 0x0200, that is 2.56 us at 200 MHz).
+Unit: CK periods.
+Limits: values 1 to 15 are illegal (cfg_valid = 0); rescale it when hr_clk.ck_div changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="20.5" customHeight="1">
+      <c r="A213" s="22" t="inlineStr">
+        <is>
+          <t>hr_d1_idr</t>
+        </is>
+      </c>
+      <c r="B213" s="22" t="inlineStr">
+        <is>
+          <t>0x224</t>
+        </is>
+      </c>
+      <c r="C213" s="22" t="n"/>
+      <c r="D213" s="22" t="n"/>
+      <c r="E213" s="22" t="n"/>
+      <c r="F213" s="22" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="G213" s="22" t="inlineStr">
+        <is>
+          <t>Chip select 1 device ID0 register. Holds the ID0 value that the controller read from the device at start-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="38" customHeight="1">
+      <c r="A214" s="21" t="n"/>
+      <c r="B214" s="21" t="n"/>
+      <c r="C214" s="21" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D214" s="21" t="inlineStr">
+        <is>
+          <t>[31:16]</t>
+        </is>
+      </c>
+      <c r="E214" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F214" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G214" s="21" t="inlineStr">
+        <is>
+          <t>This field is unused.
+Read-as-zero and write-ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="213" customHeight="1">
+      <c r="A215" s="21" t="n"/>
+      <c r="B215" s="21" t="n"/>
+      <c r="C215" s="21" t="inlineStr">
+        <is>
+          <t>id0_act</t>
+        </is>
+      </c>
+      <c r="D215" s="21" t="inlineStr">
+        <is>
+          <t>[15:0]</t>
+        </is>
+      </c>
+      <c r="E215" s="21" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F215" s="21" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G215" s="21" t="inlineStr">
+        <is>
+          <t>Actual ID0. The 16-bit ID0 register of the device (row address bits, column address bits and manufacturer) read by the controller after start-up.
+Usage: read-only; valid after hr_sts.init_done = 1; compare it with the datasheet of the device, or read ID0 again at any time through the device command port (hr_cmd with the ID0 register address in hr_cmd_addr).
+Values:
+0x0000 to 0xFFFF ID0 value read from the device.
+Unit: none.
+Limits: 0x0000 before the start-up read.</t>
         </is>
       </c>
     </row>
